--- a/FPL_League_506845_GW1_Full_Season.xlsx
+++ b/FPL_League_506845_GW1_Full_Season.xlsx
@@ -431,15 +431,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP45"/>
+  <dimension ref="A1:AR45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="27" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
@@ -476,6 +476,8 @@
     <col width="11" customWidth="1" min="40" max="40"/>
     <col width="11" customWidth="1" min="41" max="41"/>
     <col width="11" customWidth="1" min="42" max="42"/>
+    <col width="11" customWidth="1" min="43" max="43"/>
+    <col width="11" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -501,190 +503,200 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>กัปตัน GW1 (Captain)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>สำรอง GW1 (Bench)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>GW1</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>GW2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>GW3</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>GW4</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>GW5</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>GW6</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>GW7</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>GW8</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>GW9</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>GW10</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>GW11</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>GW12</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>GW13</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>GW14</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>GW15</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>GW16</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>GW17</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>GW18</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>GW19</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>GW20</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>GW21</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>GW22</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>GW23</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>GW24</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>GW25</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>GW26</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>GW27</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>GW28</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>GW29</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>GW30</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>GW31</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>GW32</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>GW33</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>GW34</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>GW35</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>GW36</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>GW37</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>GW38</t>
         </is>
@@ -707,11 +719,17 @@
       <c r="D2" t="n">
         <v>64</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>B.Fernandes (4 pts)</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>17</v>
+      </c>
+      <c r="G2" t="n">
         <v>64</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
@@ -747,6 +765,8 @@
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -765,11 +785,17 @@
       <c r="D3" t="n">
         <v>60</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>B.Fernandes (4 pts)</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>27</v>
+      </c>
+      <c r="G3" t="n">
         <v>60</v>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
@@ -805,6 +831,8 @@
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -823,11 +851,17 @@
       <c r="D4" t="n">
         <v>54</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G4" t="n">
         <v>54</v>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
@@ -863,6 +897,8 @@
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -881,11 +917,17 @@
       <c r="D5" t="n">
         <v>52</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Mbeumo (4 pts)</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" t="n">
         <v>52</v>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -921,6 +963,8 @@
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -939,11 +983,17 @@
       <c r="D6" t="n">
         <v>51</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" t="n">
         <v>51</v>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
@@ -979,6 +1029,8 @@
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -997,11 +1049,17 @@
       <c r="D7" t="n">
         <v>49</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Rogers (0 pts)</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" t="n">
         <v>49</v>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
@@ -1037,6 +1095,8 @@
       <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1044,22 +1104,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Klong 5 Rovers</t>
+          <t>Nuttawut's Team</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Guy Klong5</t>
+          <t>Nuttawut Chutipong</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>49</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Saka (18 pts)</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" t="n">
         <v>49</v>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
@@ -1095,6 +1161,8 @@
       <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1102,22 +1170,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nuttawut's Team</t>
+          <t>Klong 5 Rovers</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Nuttawut Chutipong</t>
+          <t>Guy Klong5</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>49</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>9</v>
+      </c>
+      <c r="G9" t="n">
         <v>49</v>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
@@ -1153,6 +1227,8 @@
       <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1171,11 +1247,17 @@
       <c r="D10" t="n">
         <v>48</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>B.Fernandes (4 pts)</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>9</v>
+      </c>
+      <c r="G10" t="n">
         <v>48</v>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
@@ -1211,6 +1293,8 @@
       <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1229,11 +1313,17 @@
       <c r="D11" t="n">
         <v>46</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" t="n">
         <v>46</v>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
@@ -1269,6 +1359,8 @@
       <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1287,11 +1379,17 @@
       <c r="D12" t="n">
         <v>45</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>7</v>
+      </c>
+      <c r="G12" t="n">
         <v>45</v>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
@@ -1327,6 +1425,8 @@
       <c r="AN12" t="inlineStr"/>
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1345,11 +1445,17 @@
       <c r="D13" t="n">
         <v>45</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>12</v>
+      </c>
+      <c r="G13" t="n">
         <v>45</v>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
@@ -1385,6 +1491,8 @@
       <c r="AN13" t="inlineStr"/>
       <c r="AO13" t="inlineStr"/>
       <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1392,22 +1500,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PheT9</t>
+          <t>Lek C King</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Phachara Wannarat</t>
+          <t>Banyawake Tharnthong</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>43</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Rice (6 pts)</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="n">
         <v>43</v>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
@@ -1443,6 +1557,8 @@
       <c r="AN14" t="inlineStr"/>
       <c r="AO14" t="inlineStr"/>
       <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1461,11 +1577,17 @@
       <c r="D15" t="n">
         <v>43</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Gabriel (10 pts)</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>5</v>
+      </c>
+      <c r="G15" t="n">
         <v>43</v>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
@@ -1501,6 +1623,8 @@
       <c r="AN15" t="inlineStr"/>
       <c r="AO15" t="inlineStr"/>
       <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1508,22 +1632,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lek C King</t>
+          <t>PheT9</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Banyawake Tharnthong</t>
+          <t>Phachara Wannarat</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>43</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>B.Fernandes (4 pts)</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>12</v>
+      </c>
+      <c r="G16" t="n">
         <v>43</v>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
@@ -1559,6 +1689,8 @@
       <c r="AN16" t="inlineStr"/>
       <c r="AO16" t="inlineStr"/>
       <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1566,22 +1698,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Aofmook Fc</t>
+          <t>DATE26th</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tuntawat Juntun</t>
+          <t>Prarunya Kamahayung</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>39</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Saka (18 pts)</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>7</v>
+      </c>
+      <c r="G17" t="n">
         <v>39</v>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
@@ -1617,6 +1755,8 @@
       <c r="AN17" t="inlineStr"/>
       <c r="AO17" t="inlineStr"/>
       <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1624,22 +1764,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Yenzo</t>
+          <t>ทีมของ Kritsada</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Xabi Alonso</t>
+          <t>Kritsada saejueng</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>39</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>B.Fernandes (4 pts)</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>12</v>
+      </c>
+      <c r="G18" t="n">
         <v>39</v>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
@@ -1675,6 +1821,8 @@
       <c r="AN18" t="inlineStr"/>
       <c r="AO18" t="inlineStr"/>
       <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1682,22 +1830,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DATE26th</t>
+          <t>Yenzo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Prarunya Kamahayung</t>
+          <t>Xabi Alonso</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>39</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>10</v>
+      </c>
+      <c r="G19" t="n">
         <v>39</v>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
@@ -1733,6 +1887,8 @@
       <c r="AN19" t="inlineStr"/>
       <c r="AO19" t="inlineStr"/>
       <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1740,22 +1896,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ทีมของ Kritsada</t>
+          <t>Aofmook Fc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kritsada saejueng</t>
+          <t>Tuntawat Juntun</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>39</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Raya (12 pts)</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>5</v>
+      </c>
+      <c r="G20" t="n">
         <v>39</v>
       </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
@@ -1791,6 +1953,8 @@
       <c r="AN20" t="inlineStr"/>
       <c r="AO20" t="inlineStr"/>
       <c r="AP20" t="inlineStr"/>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1809,11 +1973,17 @@
       <c r="D21" t="n">
         <v>37</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>O'Reilly (4 pts)</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>5</v>
+      </c>
+      <c r="G21" t="n">
         <v>37</v>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
@@ -1849,6 +2019,8 @@
       <c r="AN21" t="inlineStr"/>
       <c r="AO21" t="inlineStr"/>
       <c r="AP21" t="inlineStr"/>
+      <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1867,11 +2039,17 @@
       <c r="D22" t="n">
         <v>36</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>6</v>
+      </c>
+      <c r="G22" t="n">
         <v>36</v>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
@@ -1907,6 +2085,8 @@
       <c r="AN22" t="inlineStr"/>
       <c r="AO22" t="inlineStr"/>
       <c r="AP22" t="inlineStr"/>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1925,11 +2105,17 @@
       <c r="D23" t="n">
         <v>36</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>25</v>
+      </c>
+      <c r="G23" t="n">
         <v>36</v>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
@@ -1965,6 +2151,8 @@
       <c r="AN23" t="inlineStr"/>
       <c r="AO23" t="inlineStr"/>
       <c r="AP23" t="inlineStr"/>
+      <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1983,11 +2171,17 @@
       <c r="D24" t="n">
         <v>36</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>29</v>
+      </c>
+      <c r="G24" t="n">
         <v>36</v>
       </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
@@ -2023,6 +2217,8 @@
       <c r="AN24" t="inlineStr"/>
       <c r="AO24" t="inlineStr"/>
       <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2041,11 +2237,17 @@
       <c r="D25" t="n">
         <v>35</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>3</v>
+      </c>
+      <c r="G25" t="n">
         <v>35</v>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
@@ -2081,6 +2283,8 @@
       <c r="AN25" t="inlineStr"/>
       <c r="AO25" t="inlineStr"/>
       <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2099,11 +2303,17 @@
       <c r="D26" t="n">
         <v>34</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Gyökeres (0 pts)</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>5</v>
+      </c>
+      <c r="G26" t="n">
         <v>34</v>
       </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
@@ -2139,6 +2349,8 @@
       <c r="AN26" t="inlineStr"/>
       <c r="AO26" t="inlineStr"/>
       <c r="AP26" t="inlineStr"/>
+      <c r="AQ26" t="inlineStr"/>
+      <c r="AR26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2157,11 +2369,17 @@
       <c r="D27" t="n">
         <v>33</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>18</v>
+      </c>
+      <c r="G27" t="n">
         <v>33</v>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
@@ -2197,6 +2415,8 @@
       <c r="AN27" t="inlineStr"/>
       <c r="AO27" t="inlineStr"/>
       <c r="AP27" t="inlineStr"/>
+      <c r="AQ27" t="inlineStr"/>
+      <c r="AR27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2204,22 +2424,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Winning Standard FC</t>
+          <t>รถซื้อแกง จะแรงได้ไง</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Maytapat Yurawattarapon</t>
+          <t>Nuttapong Limadisai</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>32</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>15</v>
+      </c>
+      <c r="G28" t="n">
         <v>32</v>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
@@ -2255,6 +2481,8 @@
       <c r="AN28" t="inlineStr"/>
       <c r="AO28" t="inlineStr"/>
       <c r="AP28" t="inlineStr"/>
+      <c r="AQ28" t="inlineStr"/>
+      <c r="AR28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2262,22 +2490,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>N. DE JOE</t>
+          <t>Winning Standard FC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nawapon Dechabun</t>
+          <t>Maytapat Yurawattarapon</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v>32</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>B.Fernandes (4 pts)</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>6</v>
+      </c>
+      <c r="G29" t="n">
         <v>32</v>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
@@ -2313,6 +2547,8 @@
       <c r="AN29" t="inlineStr"/>
       <c r="AO29" t="inlineStr"/>
       <c r="AP29" t="inlineStr"/>
+      <c r="AQ29" t="inlineStr"/>
+      <c r="AR29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2320,22 +2556,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>รถซื้อแกง จะแรงได้ไง</t>
+          <t>N. DE JOE</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nuttapong Limadisai</t>
+          <t>Nawapon Dechabun</t>
         </is>
       </c>
       <c r="D30" t="n">
         <v>32</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>3</v>
+      </c>
+      <c r="G30" t="n">
         <v>32</v>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
@@ -2371,6 +2613,8 @@
       <c r="AN30" t="inlineStr"/>
       <c r="AO30" t="inlineStr"/>
       <c r="AP30" t="inlineStr"/>
+      <c r="AQ30" t="inlineStr"/>
+      <c r="AR30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2389,11 +2633,17 @@
       <c r="D31" t="n">
         <v>31</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Isak (4 pts)</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>8</v>
+      </c>
+      <c r="G31" t="n">
         <v>31</v>
       </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
@@ -2429,6 +2679,8 @@
       <c r="AN31" t="inlineStr"/>
       <c r="AO31" t="inlineStr"/>
       <c r="AP31" t="inlineStr"/>
+      <c r="AQ31" t="inlineStr"/>
+      <c r="AR31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2447,11 +2699,17 @@
       <c r="D32" t="n">
         <v>31</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Rice (6 pts)</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" t="n">
         <v>31</v>
       </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
@@ -2487,6 +2745,8 @@
       <c r="AN32" t="inlineStr"/>
       <c r="AO32" t="inlineStr"/>
       <c r="AP32" t="inlineStr"/>
+      <c r="AQ32" t="inlineStr"/>
+      <c r="AR32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2505,11 +2765,17 @@
       <c r="D33" t="n">
         <v>30</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>João Pedro (0 pts)</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G33" t="n">
         <v>30</v>
       </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
@@ -2545,6 +2811,8 @@
       <c r="AN33" t="inlineStr"/>
       <c r="AO33" t="inlineStr"/>
       <c r="AP33" t="inlineStr"/>
+      <c r="AQ33" t="inlineStr"/>
+      <c r="AR33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2563,11 +2831,17 @@
       <c r="D34" t="n">
         <v>30</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>B.Fernandes (4 pts)</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G34" t="n">
         <v>30</v>
       </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
@@ -2603,6 +2877,8 @@
       <c r="AN34" t="inlineStr"/>
       <c r="AO34" t="inlineStr"/>
       <c r="AP34" t="inlineStr"/>
+      <c r="AQ34" t="inlineStr"/>
+      <c r="AR34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2621,11 +2897,17 @@
       <c r="D35" t="n">
         <v>29</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>11</v>
+      </c>
+      <c r="G35" t="n">
         <v>29</v>
       </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
@@ -2661,6 +2943,8 @@
       <c r="AN35" t="inlineStr"/>
       <c r="AO35" t="inlineStr"/>
       <c r="AP35" t="inlineStr"/>
+      <c r="AQ35" t="inlineStr"/>
+      <c r="AR35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2679,11 +2963,17 @@
       <c r="D36" t="n">
         <v>29</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>B.Fernandes (4 pts)</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>7</v>
+      </c>
+      <c r="G36" t="n">
         <v>29</v>
       </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
@@ -2719,6 +3009,8 @@
       <c r="AN36" t="inlineStr"/>
       <c r="AO36" t="inlineStr"/>
       <c r="AP36" t="inlineStr"/>
+      <c r="AQ36" t="inlineStr"/>
+      <c r="AR36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2726,22 +3018,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Wayuchocolate</t>
+          <t>Marcomon FC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ponlakit Choeychang</t>
+          <t>Montri Chamchuklin</t>
         </is>
       </c>
       <c r="D37" t="n">
         <v>28</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Semenyo (4 pts)</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>14</v>
+      </c>
+      <c r="G37" t="n">
         <v>28</v>
       </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
@@ -2777,6 +3075,8 @@
       <c r="AN37" t="inlineStr"/>
       <c r="AO37" t="inlineStr"/>
       <c r="AP37" t="inlineStr"/>
+      <c r="AQ37" t="inlineStr"/>
+      <c r="AR37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2784,22 +3084,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Pending Moderation</t>
+          <t>US TM</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sukit Mattanaweerapong</t>
+          <t>rawat rummamai</t>
         </is>
       </c>
       <c r="D38" t="n">
         <v>28</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Isak (4 pts)</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>2</v>
+      </c>
+      <c r="G38" t="n">
         <v>28</v>
       </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
@@ -2835,6 +3141,8 @@
       <c r="AN38" t="inlineStr"/>
       <c r="AO38" t="inlineStr"/>
       <c r="AP38" t="inlineStr"/>
+      <c r="AQ38" t="inlineStr"/>
+      <c r="AR38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2842,22 +3150,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>US TM</t>
+          <t>Pending Moderation</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>rawat rummamai</t>
+          <t>Sukit Mattanaweerapong</t>
         </is>
       </c>
       <c r="D39" t="n">
         <v>28</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>7</v>
+      </c>
+      <c r="G39" t="n">
         <v>28</v>
       </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
@@ -2893,6 +3207,8 @@
       <c r="AN39" t="inlineStr"/>
       <c r="AO39" t="inlineStr"/>
       <c r="AP39" t="inlineStr"/>
+      <c r="AQ39" t="inlineStr"/>
+      <c r="AR39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2900,22 +3216,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Marcomon FC</t>
+          <t>Wayuchocolate</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Montri Chamchuklin</t>
+          <t>Ponlakit Choeychang</t>
         </is>
       </c>
       <c r="D40" t="n">
         <v>28</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Anderson (4 pts)</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" t="n">
         <v>28</v>
       </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
@@ -2951,6 +3273,8 @@
       <c r="AN40" t="inlineStr"/>
       <c r="AO40" t="inlineStr"/>
       <c r="AP40" t="inlineStr"/>
+      <c r="AQ40" t="inlineStr"/>
+      <c r="AR40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2969,11 +3293,17 @@
       <c r="D41" t="n">
         <v>26</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>10</v>
+      </c>
+      <c r="G41" t="n">
         <v>26</v>
       </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
@@ -3009,6 +3339,8 @@
       <c r="AN41" t="inlineStr"/>
       <c r="AO41" t="inlineStr"/>
       <c r="AP41" t="inlineStr"/>
+      <c r="AQ41" t="inlineStr"/>
+      <c r="AR41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3016,22 +3348,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>C-KING</t>
+          <t>Okaynaja</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Theera Tiawilai</t>
+          <t>Sir Okaynaja</t>
         </is>
       </c>
       <c r="D42" t="n">
         <v>25</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>B.Fernandes (4 pts)</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>11</v>
+      </c>
+      <c r="G42" t="n">
         <v>25</v>
       </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
@@ -3067,6 +3405,8 @@
       <c r="AN42" t="inlineStr"/>
       <c r="AO42" t="inlineStr"/>
       <c r="AP42" t="inlineStr"/>
+      <c r="AQ42" t="inlineStr"/>
+      <c r="AR42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3074,22 +3414,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Okaynaja</t>
+          <t>C-KING</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sir Okaynaja</t>
+          <t>Theera Tiawilai</t>
         </is>
       </c>
       <c r="D43" t="n">
         <v>25</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>B.Fernandes (4 pts)</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>3</v>
+      </c>
+      <c r="G43" t="n">
         <v>25</v>
       </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
@@ -3125,6 +3471,8 @@
       <c r="AN43" t="inlineStr"/>
       <c r="AO43" t="inlineStr"/>
       <c r="AP43" t="inlineStr"/>
+      <c r="AQ43" t="inlineStr"/>
+      <c r="AR43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3143,11 +3491,17 @@
       <c r="D44" t="n">
         <v>20</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>B.Fernandes (4 pts)</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>8</v>
+      </c>
+      <c r="G44" t="n">
         <v>20</v>
       </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
@@ -3183,6 +3537,8 @@
       <c r="AN44" t="inlineStr"/>
       <c r="AO44" t="inlineStr"/>
       <c r="AP44" t="inlineStr"/>
+      <c r="AQ44" t="inlineStr"/>
+      <c r="AR44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3201,11 +3557,17 @@
       <c r="D45" t="n">
         <v>12</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>9</v>
+      </c>
+      <c r="G45" t="n">
         <v>12</v>
       </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
@@ -3241,6 +3603,8 @@
       <c r="AN45" t="inlineStr"/>
       <c r="AO45" t="inlineStr"/>
       <c r="AP45" t="inlineStr"/>
+      <c r="AQ45" t="inlineStr"/>
+      <c r="AR45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3253,18 +3617,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="82" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="82" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3290,27 +3656,37 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>คะแนนสุทธิ GW1 (แจกรางวัล)</t>
+          <t>คะแนนสุทธิ GW1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>กัปตัน</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>แต้มตัวสำรอง (Bench)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>คะแนน FPL ทางการ</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>ชิปที่ใช้ใน GW1</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>แต้มที่ถูกตัดออก</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>เหตุผล / รายละเอียด</t>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>กฎตัดสิน / หมายเหตุ</t>
         </is>
       </c>
     </row>
@@ -3334,20 +3710,28 @@
       <c r="E2" t="n">
         <v>52</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>© Mbeumo (4 pts)</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" t="n">
         <v>52</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
         </is>
@@ -3362,31 +3746,39 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>sirxpxk_</t>
+          <t>Nuttawut's Team</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>sirxpxk _</t>
+          <t>Nuttawut Chutipong</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>49</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>© Saka (18 pts)</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" t="n">
         <v>49</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
         </is>
@@ -3412,22 +3804,30 @@
       <c r="E4" t="n">
         <v>49</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>© Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H4" t="n">
         <v>49</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>แพ้ไทเบรกเกอร์กัปตัน (4 vs 18)</t>
         </is>
       </c>
     </row>
@@ -3440,33 +3840,41 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Nuttawut's Team</t>
+          <t>sirxpxk_</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Nuttawut Chutipong</t>
+          <t>sirxpxk _</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>49</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>© Rogers (0 pts)</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" t="n">
         <v>49</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>แพ้ไทเบรกเกอร์กัปตัน (0 vs 4)</t>
         </is>
       </c>
     </row>
@@ -3490,20 +3898,28 @@
       <c r="E6" t="n">
         <v>48</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>© B.Fernandes (4 pts)</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H6" t="n">
         <v>48</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
         </is>
@@ -3529,20 +3945,28 @@
       <c r="E7" t="n">
         <v>47</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>© B.Fernandes (4 pts)</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>17</v>
+      </c>
+      <c r="H7" t="n">
         <v>64</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Bench Boost (BB)</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>ใช้ BB -&gt; หักสำรอง 4 คน [Kinsky(2), Kerkez(0), Xhaka(9), Bogle(6)]</t>
         </is>
@@ -3568,20 +3992,28 @@
       <c r="E8" t="n">
         <v>46</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>© Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" t="n">
         <v>46</v>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
         </is>
@@ -3592,37 +4024,45 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>IS_AK 18</t>
+          <t>Wat Nong+ Pla NiL FC</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>อิทธิวัฒน์ คำภา</t>
+          <t>Piyabut Promrungruang</t>
         </is>
       </c>
       <c r="E9" t="n">
         <v>45</v>
       </c>
-      <c r="F9" t="n">
-        <v>51</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Bench Boost (BB)</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-6</t>
-        </is>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>© Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>12</v>
+      </c>
+      <c r="H9" t="n">
+        <v>45</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ใช้ BB -&gt; หักสำรอง 4 คน [Kinsky(2), João Pedro(0), Schade(3), Maguire(1)]</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
         </is>
       </c>
     </row>
@@ -3646,22 +4086,30 @@
       <c r="E10" t="n">
         <v>45</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>© Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>7</v>
+      </c>
+      <c r="H10" t="n">
         <v>45</v>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>แพ้ไทเบรกเกอร์สำรอง (7 vs 12)</t>
         </is>
       </c>
     </row>
@@ -3670,37 +4118,45 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wat Nong+ Pla NiL FC</t>
+          <t>IS_AK 18</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Piyabut Promrungruang</t>
+          <t>อิทธิวัฒน์ คำภา</t>
         </is>
       </c>
       <c r="E11" t="n">
         <v>45</v>
       </c>
-      <c r="F11" t="n">
-        <v>45</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>© Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>6</v>
+      </c>
+      <c r="H11" t="n">
+        <v>51</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
+          <t>Bench Boost (BB)</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-6</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>แพ้ไทเบรกเกอร์สำรอง (6 vs 7)</t>
         </is>
       </c>
     </row>
@@ -3724,20 +4180,28 @@
       <c r="E12" t="n">
         <v>43</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>© Gabriel (10 pts)</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H12" t="n">
         <v>43</v>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
         </is>
@@ -3763,22 +4227,30 @@
       <c r="E13" t="n">
         <v>43</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>© Rice (6 pts)</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="n">
         <v>43</v>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>แพ้ไทเบรกเกอร์กัปตัน (6 vs 10)</t>
         </is>
       </c>
     </row>
@@ -3791,31 +4263,39 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Aofmook Fc</t>
+          <t>DATE26th</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Tuntawat Juntun</t>
+          <t>Prarunya Kamahayung</t>
         </is>
       </c>
       <c r="E14" t="n">
         <v>39</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>© Saka (18 pts)</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>7</v>
+      </c>
+      <c r="H14" t="n">
         <v>39</v>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
         </is>
@@ -3830,33 +4310,41 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Yenzo</t>
+          <t>Aofmook Fc</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Xabi Alonso</t>
+          <t>Tuntawat Juntun</t>
         </is>
       </c>
       <c r="E15" t="n">
         <v>39</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>© Raya (12 pts)</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>5</v>
+      </c>
+      <c r="H15" t="n">
         <v>39</v>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>แพ้ไทเบรกเกอร์กัปตัน (12 vs 18)</t>
         </is>
       </c>
     </row>
@@ -3869,33 +4357,41 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DATE26th</t>
+          <t>ทีมของ Kritsada</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Prarunya Kamahayung</t>
+          <t>Kritsada saejueng</t>
         </is>
       </c>
       <c r="E16" t="n">
         <v>39</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>© B.Fernandes (4 pts)</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>12</v>
+      </c>
+      <c r="H16" t="n">
         <v>39</v>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>แพ้ไทเบรกเกอร์กัปตัน (4 vs 12)</t>
         </is>
       </c>
     </row>
@@ -3908,33 +4404,41 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ทีมของ Kritsada</t>
+          <t>Yenzo</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Kritsada saejueng</t>
+          <t>Xabi Alonso</t>
         </is>
       </c>
       <c r="E17" t="n">
         <v>39</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>© Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>10</v>
+      </c>
+      <c r="H17" t="n">
         <v>39</v>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>แพ้ไทเบรกเกอร์สำรอง (10 vs 12)</t>
         </is>
       </c>
     </row>
@@ -3958,20 +4462,28 @@
       <c r="E18" t="n">
         <v>37</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>© Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>17</v>
+      </c>
+      <c r="H18" t="n">
         <v>54</v>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>Bench Boost (BB)</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>ใช้ BB -&gt; หักสำรอง 4 คน [Pickford(7), Richards(3), Jensen(6), Isidor(1)]</t>
         </is>
@@ -3997,22 +4509,30 @@
       <c r="E19" t="n">
         <v>37</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>© O'Reilly (4 pts)</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H19" t="n">
         <v>37</v>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>แพ้ไทเบรกเกอร์สำรอง (5 vs 17)</t>
         </is>
       </c>
     </row>
@@ -4025,31 +4545,39 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pimson Team</t>
+          <t>ผู้บ่าวไทบ้าน</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Chanwit Pimson</t>
+          <t>Thanit Sophajit</t>
         </is>
       </c>
       <c r="E20" t="n">
         <v>36</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>© Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>29</v>
+      </c>
+      <c r="H20" t="n">
         <v>36</v>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
         </is>
@@ -4075,22 +4603,30 @@
       <c r="E21" t="n">
         <v>36</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>© Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>25</v>
+      </c>
+      <c r="H21" t="n">
         <v>36</v>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>แพ้ไทเบรกเกอร์สำรอง (25 vs 29)</t>
         </is>
       </c>
     </row>
@@ -4103,33 +4639,41 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ผู้บ่าวไทบ้าน</t>
+          <t>Pimson Team</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Thanit Sophajit</t>
+          <t>Chanwit Pimson</t>
         </is>
       </c>
       <c r="E22" t="n">
         <v>36</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>© Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>6</v>
+      </c>
+      <c r="H22" t="n">
         <v>36</v>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>แพ้ไทเบรกเกอร์สำรอง (6 vs 25)</t>
         </is>
       </c>
     </row>
@@ -4153,20 +4697,28 @@
       <c r="E23" t="n">
         <v>35</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>© Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>3</v>
+      </c>
+      <c r="H23" t="n">
         <v>35</v>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
         </is>
@@ -4192,20 +4744,28 @@
       <c r="E24" t="n">
         <v>34</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>© Gyökeres (0 pts)</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>5</v>
+      </c>
+      <c r="H24" t="n">
         <v>34</v>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
         </is>
@@ -4231,20 +4791,28 @@
       <c r="E25" t="n">
         <v>33</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>© B.Fernandes (4 pts)</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>27</v>
+      </c>
+      <c r="H25" t="n">
         <v>60</v>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>Bench Boost (BB)</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>-27</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>ใช้ BB -&gt; หักสำรอง 4 คน [Verbruggen(6), João Pedro(0), Gakpo(12), Gvardiol(9)]</t>
         </is>
@@ -4270,22 +4838,30 @@
       <c r="E26" t="n">
         <v>33</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>© Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>18</v>
+      </c>
+      <c r="H26" t="n">
         <v>33</v>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>แพ้ไทเบรกเกอร์สำรอง (18 vs 27)</t>
         </is>
       </c>
     </row>
@@ -4298,31 +4874,39 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Winning Standard FC</t>
+          <t>รถซื้อแกง จะแรงได้ไง</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Maytapat Yurawattarapon</t>
+          <t>Nuttapong Limadisai</t>
         </is>
       </c>
       <c r="E27" t="n">
         <v>32</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>© Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>15</v>
+      </c>
+      <c r="H27" t="n">
         <v>32</v>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
         </is>
@@ -4337,33 +4921,41 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>N. DE JOE</t>
+          <t>Winning Standard FC</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Nawapon Dechabun</t>
+          <t>Maytapat Yurawattarapon</t>
         </is>
       </c>
       <c r="E28" t="n">
         <v>32</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>© B.Fernandes (4 pts)</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>6</v>
+      </c>
+      <c r="H28" t="n">
         <v>32</v>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>แพ้ไทเบรกเกอร์สำรอง (6 vs 15)</t>
         </is>
       </c>
     </row>
@@ -4376,33 +4968,41 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>รถซื้อแกง จะแรงได้ไง</t>
+          <t>N. DE JOE</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Nuttapong Limadisai</t>
+          <t>Nawapon Dechabun</t>
         </is>
       </c>
       <c r="E29" t="n">
         <v>32</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>© Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>3</v>
+      </c>
+      <c r="H29" t="n">
         <v>32</v>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>แพ้ไทเบรกเกอร์สำรอง (3 vs 6)</t>
         </is>
       </c>
     </row>
@@ -4411,37 +5011,45 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PheT9</t>
+          <t>Aruch's Team</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Phachara Wannarat</t>
+          <t>Aruch Changthong</t>
         </is>
       </c>
       <c r="E30" t="n">
         <v>31</v>
       </c>
-      <c r="F30" t="n">
-        <v>43</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Bench Boost (BB)</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>-12</t>
-        </is>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>© Rice (6 pts)</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>2</v>
+      </c>
+      <c r="H30" t="n">
+        <v>31</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>ใช้ BB -&gt; หักสำรอง 4 คน [Lammens(1), Palestra(0), Davis(2), Ndiaye(9)]</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
         </is>
       </c>
     </row>
@@ -4450,37 +5058,45 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pending Moderation</t>
+          <t>PheT9</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Pongsit Srisorn</t>
+          <t>Phachara Wannarat</t>
         </is>
       </c>
       <c r="E31" t="n">
         <v>31</v>
       </c>
-      <c r="F31" t="n">
-        <v>31</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>© B.Fernandes (4 pts)</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>12</v>
+      </c>
+      <c r="H31" t="n">
+        <v>43</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
+          <t>Bench Boost (BB)</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>-12</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>แพ้ไทเบรกเกอร์กัปตัน (4 vs 6)</t>
         </is>
       </c>
     </row>
@@ -4493,33 +5109,41 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Aruch's Team</t>
+          <t>Pending Moderation</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Aruch Changthong</t>
+          <t>Pongsit Srisorn</t>
         </is>
       </c>
       <c r="E32" t="n">
         <v>31</v>
       </c>
-      <c r="F32" t="n">
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>© Isak (4 pts)</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>8</v>
+      </c>
+      <c r="H32" t="n">
         <v>31</v>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>แพ้ไทเบรกเกอร์สำรอง (8 vs 12)</t>
         </is>
       </c>
     </row>
@@ -4532,31 +5156,39 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PS</t>
+          <t>eakachai@romeO</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Pongnarin Savangvong</t>
+          <t>Eakachai Hamhomvong</t>
         </is>
       </c>
       <c r="E33" t="n">
         <v>30</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>© B.Fernandes (4 pts)</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>3</v>
+      </c>
+      <c r="H33" t="n">
         <v>30</v>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
         </is>
@@ -4571,33 +5203,41 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>eakachai@romeO</t>
+          <t>PS</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Eakachai Hamhomvong</t>
+          <t>Pongnarin Savangvong</t>
         </is>
       </c>
       <c r="E34" t="n">
         <v>30</v>
       </c>
-      <c r="F34" t="n">
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>© João Pedro (0 pts)</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H34" t="n">
         <v>30</v>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>แพ้ไทเบรกเกอร์กัปตัน (0 vs 4)</t>
         </is>
       </c>
     </row>
@@ -4621,20 +5261,28 @@
       <c r="E35" t="n">
         <v>29</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>© Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>11</v>
+      </c>
+      <c r="H35" t="n">
         <v>29</v>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
         </is>
@@ -4660,22 +5308,30 @@
       <c r="E36" t="n">
         <v>29</v>
       </c>
-      <c r="F36" t="n">
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>© B.Fernandes (4 pts)</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>7</v>
+      </c>
+      <c r="H36" t="n">
         <v>29</v>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>แพ้ไทเบรกเกอร์สำรอง (7 vs 11)</t>
         </is>
       </c>
     </row>
@@ -4688,31 +5344,39 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Wayuchocolate</t>
+          <t>Marcomon FC</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ponlakit Choeychang</t>
+          <t>Montri Chamchuklin</t>
         </is>
       </c>
       <c r="E37" t="n">
         <v>28</v>
       </c>
-      <c r="F37" t="n">
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>© Semenyo (4 pts)</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>14</v>
+      </c>
+      <c r="H37" t="n">
         <v>28</v>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
         </is>
@@ -4738,22 +5402,30 @@
       <c r="E38" t="n">
         <v>28</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>© Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>7</v>
+      </c>
+      <c r="H38" t="n">
         <v>28</v>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>แพ้ไทเบรกเกอร์สำรอง (7 vs 14)</t>
         </is>
       </c>
     </row>
@@ -4777,22 +5449,30 @@
       <c r="E39" t="n">
         <v>28</v>
       </c>
-      <c r="F39" t="n">
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>© Isak (4 pts)</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>2</v>
+      </c>
+      <c r="H39" t="n">
         <v>28</v>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>แพ้ไทเบรกเกอร์สำรอง (2 vs 7)</t>
         </is>
       </c>
     </row>
@@ -4805,33 +5485,41 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Marcomon FC</t>
+          <t>Wayuchocolate</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Montri Chamchuklin</t>
+          <t>Ponlakit Choeychang</t>
         </is>
       </c>
       <c r="E40" t="n">
         <v>28</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>© Anderson (4 pts)</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" t="n">
         <v>28</v>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>แพ้ไทเบรกเกอร์สำรอง (1 vs 2)</t>
         </is>
       </c>
     </row>
@@ -4855,20 +5543,28 @@
       <c r="E41" t="n">
         <v>26</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>© Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>10</v>
+      </c>
+      <c r="H41" t="n">
         <v>26</v>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
         </is>
@@ -4883,31 +5579,39 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>C-KING</t>
+          <t>Okaynaja</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Theera Tiawilai</t>
+          <t>Sir Okaynaja</t>
         </is>
       </c>
       <c r="E42" t="n">
         <v>25</v>
       </c>
-      <c r="F42" t="n">
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>© B.Fernandes (4 pts)</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>11</v>
+      </c>
+      <c r="H42" t="n">
         <v>25</v>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
         </is>
@@ -4922,33 +5626,41 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Okaynaja</t>
+          <t>C-KING</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Sir Okaynaja</t>
+          <t>Theera Tiawilai</t>
         </is>
       </c>
       <c r="E43" t="n">
         <v>25</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>© B.Fernandes (4 pts)</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>3</v>
+      </c>
+      <c r="H43" t="n">
         <v>25</v>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>แพ้ไทเบรกเกอร์สำรอง (3 vs 11)</t>
         </is>
       </c>
     </row>
@@ -4972,20 +5684,28 @@
       <c r="E44" t="n">
         <v>20</v>
       </c>
-      <c r="F44" t="n">
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>© B.Fernandes (4 pts)</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>8</v>
+      </c>
+      <c r="H44" t="n">
         <v>20</v>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
         </is>
@@ -5011,20 +5731,28 @@
       <c r="E45" t="n">
         <v>12</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>© Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>9</v>
+      </c>
+      <c r="H45" t="n">
         <v>12</v>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
         </is>
@@ -5534,12 +6262,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Klong 5 Rovers</t>
+          <t>Nuttawut's Team</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Guy Klong5</t>
+          <t>Nuttawut Chutipong</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -5600,12 +6328,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nuttawut's Team</t>
+          <t>Klong 5 Rovers</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Nuttawut Chutipong</t>
+          <t>Guy Klong5</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -5930,12 +6658,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PheT9</t>
+          <t>Lek C King</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Phachara Wannarat</t>
+          <t>Banyawake Tharnthong</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -6062,12 +6790,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lek C King</t>
+          <t>PheT9</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Banyawake Tharnthong</t>
+          <t>Phachara Wannarat</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -6128,12 +6856,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Aofmook Fc</t>
+          <t>DATE26th</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tuntawat Juntun</t>
+          <t>Prarunya Kamahayung</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -6194,12 +6922,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Yenzo</t>
+          <t>ทีมของ Kritsada</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Xabi Alonso</t>
+          <t>Kritsada saejueng</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -6260,12 +6988,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DATE26th</t>
+          <t>Yenzo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Prarunya Kamahayung</t>
+          <t>Xabi Alonso</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -6326,12 +7054,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ทีมของ Kritsada</t>
+          <t>Aofmook Fc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kritsada saejueng</t>
+          <t>Tuntawat Juntun</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -6854,12 +7582,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Winning Standard FC</t>
+          <t>รถซื้อแกง จะแรงได้ไง</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Maytapat Yurawattarapon</t>
+          <t>Nuttapong Limadisai</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -6920,12 +7648,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>N. DE JOE</t>
+          <t>Winning Standard FC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nawapon Dechabun</t>
+          <t>Maytapat Yurawattarapon</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -6986,12 +7714,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>รถซื้อแกง จะแรงได้ไง</t>
+          <t>N. DE JOE</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nuttapong Limadisai</t>
+          <t>Nawapon Dechabun</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -7448,12 +8176,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Wayuchocolate</t>
+          <t>Marcomon FC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ponlakit Choeychang</t>
+          <t>Montri Chamchuklin</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -7514,12 +8242,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Pending Moderation</t>
+          <t>US TM</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sukit Mattanaweerapong</t>
+          <t>rawat rummamai</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -7580,12 +8308,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>US TM</t>
+          <t>Pending Moderation</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>rawat rummamai</t>
+          <t>Sukit Mattanaweerapong</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -7646,12 +8374,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Marcomon FC</t>
+          <t>Wayuchocolate</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Montri Chamchuklin</t>
+          <t>Ponlakit Choeychang</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -7778,12 +8506,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>C-KING</t>
+          <t>Okaynaja</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Theera Tiawilai</t>
+          <t>Sir Okaynaja</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -7844,12 +8572,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Okaynaja</t>
+          <t>C-KING</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sir Okaynaja</t>
+          <t>Theera Tiawilai</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -8285,12 +9013,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Klong 5 Rovers</t>
+          <t>Nuttawut's Team</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Guy Klong5</t>
+          <t>Nuttawut Chutipong</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -8317,12 +9045,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Nuttawut's Team</t>
+          <t>Klong 5 Rovers</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nuttawut Chutipong</t>
+          <t>Guy Klong5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -8477,12 +9205,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PheT9</t>
+          <t>Lek C King</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Phachara Wannarat</t>
+          <t>Banyawake Tharnthong</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -8497,7 +9225,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>GW1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -8541,12 +9269,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Lek C King</t>
+          <t>PheT9</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Banyawake Tharnthong</t>
+          <t>Phachara Wannarat</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -8561,7 +9289,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GW1</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -8573,12 +9301,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Aofmook Fc</t>
+          <t>DATE26th</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tuntawat Juntun</t>
+          <t>Prarunya Kamahayung</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -8605,12 +9333,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Yenzo</t>
+          <t>ทีมของ Kritsada</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Xabi Alonso</t>
+          <t>Kritsada saejueng</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -8637,12 +9365,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DATE26th</t>
+          <t>Yenzo</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Prarunya Kamahayung</t>
+          <t>Xabi Alonso</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -8669,12 +9397,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ทีมของ Kritsada</t>
+          <t>Aofmook Fc</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Kritsada saejueng</t>
+          <t>Tuntawat Juntun</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -8925,12 +9653,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Winning Standard FC</t>
+          <t>รถซื้อแกง จะแรงได้ไง</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Maytapat Yurawattarapon</t>
+          <t>Nuttapong Limadisai</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -8957,12 +9685,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>N. DE JOE</t>
+          <t>Winning Standard FC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nawapon Dechabun</t>
+          <t>Maytapat Yurawattarapon</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -8989,12 +9717,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>รถซื้อแกง จะแรงได้ไง</t>
+          <t>N. DE JOE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nuttapong Limadisai</t>
+          <t>Nawapon Dechabun</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -9213,12 +9941,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Wayuchocolate</t>
+          <t>Marcomon FC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ponlakit Choeychang</t>
+          <t>Montri Chamchuklin</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -9245,12 +9973,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Pending Moderation</t>
+          <t>US TM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sukit Mattanaweerapong</t>
+          <t>rawat rummamai</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -9277,12 +10005,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>US TM</t>
+          <t>Pending Moderation</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>rawat rummamai</t>
+          <t>Sukit Mattanaweerapong</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -9309,12 +10037,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Marcomon FC</t>
+          <t>Wayuchocolate</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Montri Chamchuklin</t>
+          <t>Ponlakit Choeychang</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -9373,12 +10101,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>C-KING</t>
+          <t>Okaynaja</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Theera Tiawilai</t>
+          <t>Sir Okaynaja</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -9405,12 +10133,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Okaynaja</t>
+          <t>C-KING</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Sir Okaynaja</t>
+          <t>Theera Tiawilai</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">

--- a/FPL_League_506845_GW1_Full_Season.xlsx
+++ b/FPL_League_506845_GW1_Full_Season.xlsx
@@ -431,15 +431,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR45"/>
+  <dimension ref="A1:AP45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="27" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
@@ -476,8 +476,6 @@
     <col width="11" customWidth="1" min="40" max="40"/>
     <col width="11" customWidth="1" min="41" max="41"/>
     <col width="11" customWidth="1" min="42" max="42"/>
-    <col width="11" customWidth="1" min="43" max="43"/>
-    <col width="11" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -503,200 +501,190 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>กัปตัน GW1 (Captain)</t>
+          <t>GW1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>สำรอง GW1 (Bench)</t>
+          <t>GW2</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>GW1</t>
+          <t>GW3</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>GW2</t>
+          <t>GW4</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>GW3</t>
+          <t>GW5</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>GW4</t>
+          <t>GW6</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>GW5</t>
+          <t>GW7</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>GW6</t>
+          <t>GW8</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>GW7</t>
+          <t>GW9</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>GW8</t>
+          <t>GW10</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>GW9</t>
+          <t>GW11</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>GW10</t>
+          <t>GW12</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>GW11</t>
+          <t>GW13</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>GW12</t>
+          <t>GW14</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>GW13</t>
+          <t>GW15</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>GW14</t>
+          <t>GW16</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>GW15</t>
+          <t>GW17</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>GW16</t>
+          <t>GW18</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>GW17</t>
+          <t>GW19</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>GW18</t>
+          <t>GW20</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>GW19</t>
+          <t>GW21</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>GW20</t>
+          <t>GW22</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>GW21</t>
+          <t>GW23</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>GW22</t>
+          <t>GW24</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>GW23</t>
+          <t>GW25</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>GW24</t>
+          <t>GW26</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>GW25</t>
+          <t>GW27</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>GW26</t>
+          <t>GW28</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>GW27</t>
+          <t>GW29</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>GW28</t>
+          <t>GW30</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>GW29</t>
+          <t>GW31</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>GW30</t>
+          <t>GW32</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>GW31</t>
+          <t>GW33</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>GW32</t>
+          <t>GW34</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>GW33</t>
+          <t>GW35</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>GW34</t>
+          <t>GW36</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>GW35</t>
+          <t>GW37</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>GW36</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>GW37</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>GW38</t>
         </is>
@@ -719,17 +707,11 @@
       <c r="D2" t="n">
         <v>64</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>B.Fernandes (4 pts)</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>17</v>
-      </c>
-      <c r="G2" t="n">
+      <c r="E2" t="n">
         <v>64</v>
       </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
@@ -765,8 +747,6 @@
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -785,17 +765,11 @@
       <c r="D3" t="n">
         <v>60</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>B.Fernandes (4 pts)</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>27</v>
-      </c>
-      <c r="G3" t="n">
+      <c r="E3" t="n">
         <v>60</v>
       </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
@@ -831,8 +805,6 @@
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -851,17 +823,11 @@
       <c r="D4" t="n">
         <v>54</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Haaland (4 pts)</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>17</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="E4" t="n">
         <v>54</v>
       </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
@@ -897,8 +863,6 @@
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -917,17 +881,11 @@
       <c r="D5" t="n">
         <v>52</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Mbeumo (4 pts)</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>10</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="E5" t="n">
         <v>52</v>
       </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -963,8 +921,6 @@
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -983,17 +939,11 @@
       <c r="D6" t="n">
         <v>51</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Haaland (4 pts)</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="E6" t="n">
         <v>51</v>
       </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
@@ -1029,8 +979,6 @@
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1049,17 +997,11 @@
       <c r="D7" t="n">
         <v>49</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Rogers (0 pts)</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G7" t="n">
+      <c r="E7" t="n">
         <v>49</v>
       </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
@@ -1095,8 +1037,6 @@
       <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1115,17 +1055,11 @@
       <c r="D8" t="n">
         <v>49</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Saka (18 pts)</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>3</v>
-      </c>
-      <c r="G8" t="n">
+      <c r="E8" t="n">
         <v>49</v>
       </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
@@ -1161,8 +1095,6 @@
       <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr"/>
-      <c r="AQ8" t="inlineStr"/>
-      <c r="AR8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1181,17 +1113,11 @@
       <c r="D9" t="n">
         <v>49</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Haaland (4 pts)</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>9</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="E9" t="n">
         <v>49</v>
       </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
@@ -1227,8 +1153,6 @@
       <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1247,17 +1171,11 @@
       <c r="D10" t="n">
         <v>48</v>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>B.Fernandes (4 pts)</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>9</v>
-      </c>
-      <c r="G10" t="n">
+      <c r="E10" t="n">
         <v>48</v>
       </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
@@ -1293,8 +1211,6 @@
       <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1313,17 +1229,11 @@
       <c r="D11" t="n">
         <v>46</v>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Haaland (4 pts)</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>5</v>
-      </c>
-      <c r="G11" t="n">
+      <c r="E11" t="n">
         <v>46</v>
       </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
@@ -1359,8 +1269,6 @@
       <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr"/>
-      <c r="AQ11" t="inlineStr"/>
-      <c r="AR11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1368,28 +1276,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sittinon's Team</t>
+          <t>Wat Nong+ Pla NiL FC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sittinon Temsongsai</t>
+          <t>Piyabut Promrungruang</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>45</v>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Haaland (4 pts)</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>7</v>
-      </c>
-      <c r="G12" t="n">
+      <c r="E12" t="n">
         <v>45</v>
       </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
@@ -1425,8 +1327,6 @@
       <c r="AN12" t="inlineStr"/>
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr"/>
-      <c r="AQ12" t="inlineStr"/>
-      <c r="AR12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1434,28 +1334,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Wat Nong+ Pla NiL FC</t>
+          <t>Sittinon's Team</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Piyabut Promrungruang</t>
+          <t>Sittinon Temsongsai</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>45</v>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Haaland (4 pts)</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>12</v>
-      </c>
-      <c r="G13" t="n">
+      <c r="E13" t="n">
         <v>45</v>
       </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
@@ -1491,8 +1385,6 @@
       <c r="AN13" t="inlineStr"/>
       <c r="AO13" t="inlineStr"/>
       <c r="AP13" t="inlineStr"/>
-      <c r="AQ13" t="inlineStr"/>
-      <c r="AR13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1500,28 +1392,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lek C King</t>
+          <t>RiceCooker</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Banyawake Tharnthong</t>
+          <t>Chaiwat Munkong</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>43</v>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Rice (6 pts)</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>2</v>
-      </c>
-      <c r="G14" t="n">
+      <c r="E14" t="n">
         <v>43</v>
       </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
@@ -1557,8 +1443,6 @@
       <c r="AN14" t="inlineStr"/>
       <c r="AO14" t="inlineStr"/>
       <c r="AP14" t="inlineStr"/>
-      <c r="AQ14" t="inlineStr"/>
-      <c r="AR14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1566,28 +1450,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RiceCooker</t>
+          <t>PheT9</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chaiwat Munkong</t>
+          <t>Phachara Wannarat</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>43</v>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Gabriel (10 pts)</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>5</v>
-      </c>
-      <c r="G15" t="n">
+      <c r="E15" t="n">
         <v>43</v>
       </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
@@ -1623,8 +1501,6 @@
       <c r="AN15" t="inlineStr"/>
       <c r="AO15" t="inlineStr"/>
       <c r="AP15" t="inlineStr"/>
-      <c r="AQ15" t="inlineStr"/>
-      <c r="AR15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1632,28 +1508,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PheT9</t>
+          <t>Lek C King</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Phachara Wannarat</t>
+          <t>Banyawake Tharnthong</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>43</v>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>B.Fernandes (4 pts)</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>12</v>
-      </c>
-      <c r="G16" t="n">
+      <c r="E16" t="n">
         <v>43</v>
       </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
@@ -1689,8 +1559,6 @@
       <c r="AN16" t="inlineStr"/>
       <c r="AO16" t="inlineStr"/>
       <c r="AP16" t="inlineStr"/>
-      <c r="AQ16" t="inlineStr"/>
-      <c r="AR16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1709,17 +1577,11 @@
       <c r="D17" t="n">
         <v>39</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Saka (18 pts)</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>7</v>
-      </c>
-      <c r="G17" t="n">
+      <c r="E17" t="n">
         <v>39</v>
       </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
@@ -1755,8 +1617,6 @@
       <c r="AN17" t="inlineStr"/>
       <c r="AO17" t="inlineStr"/>
       <c r="AP17" t="inlineStr"/>
-      <c r="AQ17" t="inlineStr"/>
-      <c r="AR17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1764,28 +1624,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ทีมของ Kritsada</t>
+          <t>Yenzo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kritsada saejueng</t>
+          <t>Xabi Alonso</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>39</v>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>B.Fernandes (4 pts)</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>12</v>
-      </c>
-      <c r="G18" t="n">
+      <c r="E18" t="n">
         <v>39</v>
       </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
@@ -1821,8 +1675,6 @@
       <c r="AN18" t="inlineStr"/>
       <c r="AO18" t="inlineStr"/>
       <c r="AP18" t="inlineStr"/>
-      <c r="AQ18" t="inlineStr"/>
-      <c r="AR18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1830,28 +1682,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Yenzo</t>
+          <t>Aofmook Fc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Xabi Alonso</t>
+          <t>Tuntawat Juntun</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>39</v>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Haaland (4 pts)</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>10</v>
-      </c>
-      <c r="G19" t="n">
+      <c r="E19" t="n">
         <v>39</v>
       </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
@@ -1887,8 +1733,6 @@
       <c r="AN19" t="inlineStr"/>
       <c r="AO19" t="inlineStr"/>
       <c r="AP19" t="inlineStr"/>
-      <c r="AQ19" t="inlineStr"/>
-      <c r="AR19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1896,28 +1740,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Aofmook Fc</t>
+          <t>ทีมของ Kritsada</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tuntawat Juntun</t>
+          <t>Kritsada saejueng</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>39</v>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Raya (12 pts)</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>5</v>
-      </c>
-      <c r="G20" t="n">
+      <c r="E20" t="n">
         <v>39</v>
       </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
@@ -1953,8 +1791,6 @@
       <c r="AN20" t="inlineStr"/>
       <c r="AO20" t="inlineStr"/>
       <c r="AP20" t="inlineStr"/>
-      <c r="AQ20" t="inlineStr"/>
-      <c r="AR20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1973,17 +1809,11 @@
       <c r="D21" t="n">
         <v>37</v>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>O'Reilly (4 pts)</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>5</v>
-      </c>
-      <c r="G21" t="n">
+      <c r="E21" t="n">
         <v>37</v>
       </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
@@ -2019,8 +1849,6 @@
       <c r="AN21" t="inlineStr"/>
       <c r="AO21" t="inlineStr"/>
       <c r="AP21" t="inlineStr"/>
-      <c r="AQ21" t="inlineStr"/>
-      <c r="AR21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2039,17 +1867,11 @@
       <c r="D22" t="n">
         <v>36</v>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Haaland (4 pts)</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>6</v>
-      </c>
-      <c r="G22" t="n">
+      <c r="E22" t="n">
         <v>36</v>
       </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
@@ -2085,8 +1907,6 @@
       <c r="AN22" t="inlineStr"/>
       <c r="AO22" t="inlineStr"/>
       <c r="AP22" t="inlineStr"/>
-      <c r="AQ22" t="inlineStr"/>
-      <c r="AR22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2094,28 +1914,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tengen El Paso</t>
+          <t>ผู้บ่าวไทบ้าน</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>EL Paso slow-bar Coffee</t>
+          <t>Thanit Sophajit</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>36</v>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Haaland (4 pts)</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>25</v>
-      </c>
-      <c r="G23" t="n">
+      <c r="E23" t="n">
         <v>36</v>
       </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
@@ -2151,8 +1965,6 @@
       <c r="AN23" t="inlineStr"/>
       <c r="AO23" t="inlineStr"/>
       <c r="AP23" t="inlineStr"/>
-      <c r="AQ23" t="inlineStr"/>
-      <c r="AR23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2160,28 +1972,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ผู้บ่าวไทบ้าน</t>
+          <t>Tengen El Paso</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Thanit Sophajit</t>
+          <t>EL Paso slow-bar Coffee</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>36</v>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Haaland (4 pts)</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>29</v>
-      </c>
-      <c r="G24" t="n">
+      <c r="E24" t="n">
         <v>36</v>
       </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
@@ -2217,8 +2023,6 @@
       <c r="AN24" t="inlineStr"/>
       <c r="AO24" t="inlineStr"/>
       <c r="AP24" t="inlineStr"/>
-      <c r="AQ24" t="inlineStr"/>
-      <c r="AR24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2237,17 +2041,11 @@
       <c r="D25" t="n">
         <v>35</v>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Haaland (4 pts)</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>3</v>
-      </c>
-      <c r="G25" t="n">
+      <c r="E25" t="n">
         <v>35</v>
       </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
@@ -2283,8 +2081,6 @@
       <c r="AN25" t="inlineStr"/>
       <c r="AO25" t="inlineStr"/>
       <c r="AP25" t="inlineStr"/>
-      <c r="AQ25" t="inlineStr"/>
-      <c r="AR25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2303,17 +2099,11 @@
       <c r="D26" t="n">
         <v>34</v>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Gyökeres (0 pts)</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>5</v>
-      </c>
-      <c r="G26" t="n">
+      <c r="E26" t="n">
         <v>34</v>
       </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
@@ -2349,8 +2139,6 @@
       <c r="AN26" t="inlineStr"/>
       <c r="AO26" t="inlineStr"/>
       <c r="AP26" t="inlineStr"/>
-      <c r="AQ26" t="inlineStr"/>
-      <c r="AR26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2369,17 +2157,11 @@
       <c r="D27" t="n">
         <v>33</v>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Haaland (4 pts)</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>18</v>
-      </c>
-      <c r="G27" t="n">
+      <c r="E27" t="n">
         <v>33</v>
       </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
@@ -2415,8 +2197,6 @@
       <c r="AN27" t="inlineStr"/>
       <c r="AO27" t="inlineStr"/>
       <c r="AP27" t="inlineStr"/>
-      <c r="AQ27" t="inlineStr"/>
-      <c r="AR27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2435,17 +2215,11 @@
       <c r="D28" t="n">
         <v>32</v>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Haaland (4 pts)</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>15</v>
-      </c>
-      <c r="G28" t="n">
+      <c r="E28" t="n">
         <v>32</v>
       </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
@@ -2481,8 +2255,6 @@
       <c r="AN28" t="inlineStr"/>
       <c r="AO28" t="inlineStr"/>
       <c r="AP28" t="inlineStr"/>
-      <c r="AQ28" t="inlineStr"/>
-      <c r="AR28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2490,28 +2262,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Winning Standard FC</t>
+          <t>N. DE JOE</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Maytapat Yurawattarapon</t>
+          <t>Nawapon Dechabun</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v>32</v>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>B.Fernandes (4 pts)</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>6</v>
-      </c>
-      <c r="G29" t="n">
+      <c r="E29" t="n">
         <v>32</v>
       </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
@@ -2547,8 +2313,6 @@
       <c r="AN29" t="inlineStr"/>
       <c r="AO29" t="inlineStr"/>
       <c r="AP29" t="inlineStr"/>
-      <c r="AQ29" t="inlineStr"/>
-      <c r="AR29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2556,28 +2320,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>N. DE JOE</t>
+          <t>Winning Standard FC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nawapon Dechabun</t>
+          <t>Maytapat Yurawattarapon</t>
         </is>
       </c>
       <c r="D30" t="n">
         <v>32</v>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Haaland (4 pts)</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>3</v>
-      </c>
-      <c r="G30" t="n">
+      <c r="E30" t="n">
         <v>32</v>
       </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
@@ -2613,8 +2371,6 @@
       <c r="AN30" t="inlineStr"/>
       <c r="AO30" t="inlineStr"/>
       <c r="AP30" t="inlineStr"/>
-      <c r="AQ30" t="inlineStr"/>
-      <c r="AR30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2622,28 +2378,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Pending Moderation</t>
+          <t>Aruch's Team</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pongsit Srisorn</t>
+          <t>Aruch Changthong</t>
         </is>
       </c>
       <c r="D31" t="n">
         <v>31</v>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Isak (4 pts)</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>8</v>
-      </c>
-      <c r="G31" t="n">
+      <c r="E31" t="n">
         <v>31</v>
       </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
@@ -2679,8 +2429,6 @@
       <c r="AN31" t="inlineStr"/>
       <c r="AO31" t="inlineStr"/>
       <c r="AP31" t="inlineStr"/>
-      <c r="AQ31" t="inlineStr"/>
-      <c r="AR31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2688,28 +2436,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Aruch's Team</t>
+          <t>Pending Moderation</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Aruch Changthong</t>
+          <t>Pongsit Srisorn</t>
         </is>
       </c>
       <c r="D32" t="n">
         <v>31</v>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Rice (6 pts)</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>2</v>
-      </c>
-      <c r="G32" t="n">
+      <c r="E32" t="n">
         <v>31</v>
       </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
@@ -2745,8 +2487,6 @@
       <c r="AN32" t="inlineStr"/>
       <c r="AO32" t="inlineStr"/>
       <c r="AP32" t="inlineStr"/>
-      <c r="AQ32" t="inlineStr"/>
-      <c r="AR32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2754,28 +2494,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PS</t>
+          <t>eakachai@romeO</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Pongnarin Savangvong</t>
+          <t>Eakachai Hamhomvong</t>
         </is>
       </c>
       <c r="D33" t="n">
         <v>30</v>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>João Pedro (0 pts)</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G33" t="n">
+      <c r="E33" t="n">
         <v>30</v>
       </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
@@ -2811,8 +2545,6 @@
       <c r="AN33" t="inlineStr"/>
       <c r="AO33" t="inlineStr"/>
       <c r="AP33" t="inlineStr"/>
-      <c r="AQ33" t="inlineStr"/>
-      <c r="AR33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2820,28 +2552,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>eakachai@romeO</t>
+          <t>PS</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Eakachai Hamhomvong</t>
+          <t>Pongnarin Savangvong</t>
         </is>
       </c>
       <c r="D34" t="n">
         <v>30</v>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>B.Fernandes (4 pts)</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>3</v>
-      </c>
-      <c r="G34" t="n">
+      <c r="E34" t="n">
         <v>30</v>
       </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
@@ -2877,8 +2603,6 @@
       <c r="AN34" t="inlineStr"/>
       <c r="AO34" t="inlineStr"/>
       <c r="AP34" t="inlineStr"/>
-      <c r="AQ34" t="inlineStr"/>
-      <c r="AR34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2886,28 +2610,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>KingPro</t>
+          <t>อนุบาลห้วยทับทัน</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>จิรวัฒน์ ขนอม</t>
+          <t>Chinnaarch Thanapongphasin</t>
         </is>
       </c>
       <c r="D35" t="n">
         <v>29</v>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Haaland (4 pts)</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>11</v>
-      </c>
-      <c r="G35" t="n">
+      <c r="E35" t="n">
         <v>29</v>
       </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
@@ -2943,8 +2661,6 @@
       <c r="AN35" t="inlineStr"/>
       <c r="AO35" t="inlineStr"/>
       <c r="AP35" t="inlineStr"/>
-      <c r="AQ35" t="inlineStr"/>
-      <c r="AR35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2952,28 +2668,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>อนุบาลห้วยทับทัน</t>
+          <t>KingPro</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chinnaarch Thanapongphasin</t>
+          <t>จิรวัฒน์ ขนอม</t>
         </is>
       </c>
       <c r="D36" t="n">
         <v>29</v>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>B.Fernandes (4 pts)</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>7</v>
-      </c>
-      <c r="G36" t="n">
+      <c r="E36" t="n">
         <v>29</v>
       </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
@@ -3009,8 +2719,6 @@
       <c r="AN36" t="inlineStr"/>
       <c r="AO36" t="inlineStr"/>
       <c r="AP36" t="inlineStr"/>
-      <c r="AQ36" t="inlineStr"/>
-      <c r="AR36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3029,17 +2737,11 @@
       <c r="D37" t="n">
         <v>28</v>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Semenyo (4 pts)</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>14</v>
-      </c>
-      <c r="G37" t="n">
+      <c r="E37" t="n">
         <v>28</v>
       </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
@@ -3075,8 +2777,6 @@
       <c r="AN37" t="inlineStr"/>
       <c r="AO37" t="inlineStr"/>
       <c r="AP37" t="inlineStr"/>
-      <c r="AQ37" t="inlineStr"/>
-      <c r="AR37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3084,28 +2784,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>US TM</t>
+          <t>Pending Moderation</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>rawat rummamai</t>
+          <t>Sukit Mattanaweerapong</t>
         </is>
       </c>
       <c r="D38" t="n">
         <v>28</v>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Isak (4 pts)</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>2</v>
-      </c>
-      <c r="G38" t="n">
+      <c r="E38" t="n">
         <v>28</v>
       </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
@@ -3141,8 +2835,6 @@
       <c r="AN38" t="inlineStr"/>
       <c r="AO38" t="inlineStr"/>
       <c r="AP38" t="inlineStr"/>
-      <c r="AQ38" t="inlineStr"/>
-      <c r="AR38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3150,28 +2842,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Pending Moderation</t>
+          <t>Wayuchocolate</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sukit Mattanaweerapong</t>
+          <t>Ponlakit Choeychang</t>
         </is>
       </c>
       <c r="D39" t="n">
         <v>28</v>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Haaland (4 pts)</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>7</v>
-      </c>
-      <c r="G39" t="n">
+      <c r="E39" t="n">
         <v>28</v>
       </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
@@ -3207,8 +2893,6 @@
       <c r="AN39" t="inlineStr"/>
       <c r="AO39" t="inlineStr"/>
       <c r="AP39" t="inlineStr"/>
-      <c r="AQ39" t="inlineStr"/>
-      <c r="AR39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3216,28 +2900,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Wayuchocolate</t>
+          <t>US TM</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ponlakit Choeychang</t>
+          <t>rawat rummamai</t>
         </is>
       </c>
       <c r="D40" t="n">
         <v>28</v>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Anderson (4 pts)</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" t="n">
+      <c r="E40" t="n">
         <v>28</v>
       </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
@@ -3273,8 +2951,6 @@
       <c r="AN40" t="inlineStr"/>
       <c r="AO40" t="inlineStr"/>
       <c r="AP40" t="inlineStr"/>
-      <c r="AQ40" t="inlineStr"/>
-      <c r="AR40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3293,17 +2969,11 @@
       <c r="D41" t="n">
         <v>26</v>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Haaland (4 pts)</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>10</v>
-      </c>
-      <c r="G41" t="n">
+      <c r="E41" t="n">
         <v>26</v>
       </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
@@ -3339,8 +3009,6 @@
       <c r="AN41" t="inlineStr"/>
       <c r="AO41" t="inlineStr"/>
       <c r="AP41" t="inlineStr"/>
-      <c r="AQ41" t="inlineStr"/>
-      <c r="AR41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3348,28 +3016,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Okaynaja</t>
+          <t>C-KING</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sir Okaynaja</t>
+          <t>Theera Tiawilai</t>
         </is>
       </c>
       <c r="D42" t="n">
         <v>25</v>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>B.Fernandes (4 pts)</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>11</v>
-      </c>
-      <c r="G42" t="n">
+      <c r="E42" t="n">
         <v>25</v>
       </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
@@ -3405,8 +3067,6 @@
       <c r="AN42" t="inlineStr"/>
       <c r="AO42" t="inlineStr"/>
       <c r="AP42" t="inlineStr"/>
-      <c r="AQ42" t="inlineStr"/>
-      <c r="AR42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3414,28 +3074,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>C-KING</t>
+          <t>Okaynaja</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Theera Tiawilai</t>
+          <t>Sir Okaynaja</t>
         </is>
       </c>
       <c r="D43" t="n">
         <v>25</v>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>B.Fernandes (4 pts)</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>3</v>
-      </c>
-      <c r="G43" t="n">
+      <c r="E43" t="n">
         <v>25</v>
       </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
@@ -3471,8 +3125,6 @@
       <c r="AN43" t="inlineStr"/>
       <c r="AO43" t="inlineStr"/>
       <c r="AP43" t="inlineStr"/>
-      <c r="AQ43" t="inlineStr"/>
-      <c r="AR43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3491,17 +3143,11 @@
       <c r="D44" t="n">
         <v>20</v>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>B.Fernandes (4 pts)</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>8</v>
-      </c>
-      <c r="G44" t="n">
+      <c r="E44" t="n">
         <v>20</v>
       </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
@@ -3537,8 +3183,6 @@
       <c r="AN44" t="inlineStr"/>
       <c r="AO44" t="inlineStr"/>
       <c r="AP44" t="inlineStr"/>
-      <c r="AQ44" t="inlineStr"/>
-      <c r="AR44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3557,17 +3201,11 @@
       <c r="D45" t="n">
         <v>12</v>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Haaland (4 pts)</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>9</v>
-      </c>
-      <c r="G45" t="n">
+      <c r="E45" t="n">
         <v>12</v>
       </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
@@ -3603,8 +3241,6 @@
       <c r="AN45" t="inlineStr"/>
       <c r="AO45" t="inlineStr"/>
       <c r="AP45" t="inlineStr"/>
-      <c r="AQ45" t="inlineStr"/>
-      <c r="AR45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3624,12 +3260,12 @@
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
     <col width="82" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -3656,32 +3292,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>คะแนนสุทธิ GW1</t>
+          <t>แต้มดิบ (ก่อนตัดชิป)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>กัปตัน</t>
+          <t>ชิปที่ใช้ใน GW1</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>แต้มที่ถูกตัดออก</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>คะแนนสุทธิ (แจกรางวัล)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>กัปตัน (Captain)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>แต้มตัวสำรอง (Bench)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>คะแนน FPL ทางการ</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>ชิปที่ใช้ใน GW1</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>แต้มที่ถูกตัดออก</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -3712,24 +3348,24 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>© Mbeumo (4 pts)</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>10</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H2" t="n">
         <v>52</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>© Mbeumo (4 pts)</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>10</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -3759,24 +3395,24 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>© Saka (18 pts)</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>3</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H3" t="n">
         <v>49</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>© Saka (18 pts)</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>3</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -3806,24 +3442,24 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>© Haaland (4 pts)</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>9</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H4" t="n">
         <v>49</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>© Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>9</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -3853,24 +3489,24 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>© Rogers (0 pts)</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>5</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H5" t="n">
         <v>49</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>© Rogers (0 pts)</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>5</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -3900,24 +3536,24 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>© B.Fernandes (4 pts)</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>9</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H6" t="n">
         <v>48</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>© B.Fernandes (4 pts)</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>9</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -3943,28 +3579,28 @@
         </is>
       </c>
       <c r="E7" t="n">
+        <v>64</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bench Boost (BB)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-17</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
         <v>47</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>© B.Fernandes (4 pts)</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="J7" t="n">
         <v>17</v>
-      </c>
-      <c r="H7" t="n">
-        <v>64</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Bench Boost (BB)</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>-17</t>
-        </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -3994,24 +3630,24 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>© Haaland (4 pts)</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>5</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H8" t="n">
         <v>46</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>© Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>5</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -4041,24 +3677,24 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>© Haaland (4 pts)</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>12</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H9" t="n">
         <v>45</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>© Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>12</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -4088,24 +3724,24 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>© Haaland (4 pts)</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>7</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H10" t="n">
         <v>45</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>© Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>7</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -4131,28 +3767,28 @@
         </is>
       </c>
       <c r="E11" t="n">
+        <v>51</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bench Boost (BB)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-6</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
         <v>45</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>© Haaland (4 pts)</t>
         </is>
       </c>
-      <c r="G11" t="n">
+      <c r="J11" t="n">
         <v>6</v>
-      </c>
-      <c r="H11" t="n">
-        <v>51</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Bench Boost (BB)</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>-6</t>
-        </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -4182,24 +3818,24 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>© Gabriel (10 pts)</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>5</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H12" t="n">
         <v>43</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>© Gabriel (10 pts)</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>5</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -4229,24 +3865,24 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>© Rice (6 pts)</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>2</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H13" t="n">
         <v>43</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>© Rice (6 pts)</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -4276,24 +3912,24 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>© Saka (18 pts)</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>7</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H14" t="n">
         <v>39</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>© Saka (18 pts)</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>7</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -4323,24 +3959,24 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>© Raya (12 pts)</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>5</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H15" t="n">
         <v>39</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>© Raya (12 pts)</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>5</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -4370,24 +4006,24 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>© B.Fernandes (4 pts)</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>12</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H16" t="n">
         <v>39</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>© B.Fernandes (4 pts)</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>12</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -4417,24 +4053,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>© Haaland (4 pts)</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>10</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H17" t="n">
         <v>39</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>© Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>10</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -4460,28 +4096,28 @@
         </is>
       </c>
       <c r="E18" t="n">
+        <v>54</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Bench Boost (BB)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-17</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
         <v>37</v>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>© Haaland (4 pts)</t>
         </is>
       </c>
-      <c r="G18" t="n">
+      <c r="J18" t="n">
         <v>17</v>
-      </c>
-      <c r="H18" t="n">
-        <v>54</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Bench Boost (BB)</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>-17</t>
-        </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -4511,24 +4147,24 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>© O'Reilly (4 pts)</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>5</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H19" t="n">
         <v>37</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>© O'Reilly (4 pts)</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>5</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -4558,24 +4194,24 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>© Haaland (4 pts)</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>29</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H20" t="n">
         <v>36</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>© Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>29</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -4605,24 +4241,24 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>© Haaland (4 pts)</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>25</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H21" t="n">
         <v>36</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>© Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>25</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -4652,24 +4288,24 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>© Haaland (4 pts)</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>6</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H22" t="n">
         <v>36</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>© Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>6</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -4699,24 +4335,24 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>© Haaland (4 pts)</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>3</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H23" t="n">
         <v>35</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>© Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>3</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -4746,24 +4382,24 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>© Gyökeres (0 pts)</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>5</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H24" t="n">
         <v>34</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>© Gyökeres (0 pts)</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>5</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -4789,28 +4425,28 @@
         </is>
       </c>
       <c r="E25" t="n">
+        <v>60</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Bench Boost (BB)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-27</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
         <v>33</v>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>© B.Fernandes (4 pts)</t>
         </is>
       </c>
-      <c r="G25" t="n">
+      <c r="J25" t="n">
         <v>27</v>
-      </c>
-      <c r="H25" t="n">
-        <v>60</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Bench Boost (BB)</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>-27</t>
-        </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -4840,24 +4476,24 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>© Haaland (4 pts)</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>18</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H26" t="n">
         <v>33</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>© Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>18</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -4887,24 +4523,24 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>© Haaland (4 pts)</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>15</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H27" t="n">
         <v>32</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>© Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>15</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -4934,24 +4570,24 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>© B.Fernandes (4 pts)</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>6</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H28" t="n">
         <v>32</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>© B.Fernandes (4 pts)</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>6</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -4981,24 +4617,24 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>© Haaland (4 pts)</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>3</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H29" t="n">
         <v>32</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>© Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>3</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -5028,24 +4664,24 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>© Rice (6 pts)</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>2</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H30" t="n">
         <v>31</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>© Rice (6 pts)</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>2</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -5071,28 +4707,28 @@
         </is>
       </c>
       <c r="E31" t="n">
+        <v>43</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Bench Boost (BB)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-12</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
         <v>31</v>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>© B.Fernandes (4 pts)</t>
         </is>
       </c>
-      <c r="G31" t="n">
+      <c r="J31" t="n">
         <v>12</v>
-      </c>
-      <c r="H31" t="n">
-        <v>43</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Bench Boost (BB)</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>-12</t>
-        </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -5122,24 +4758,24 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>© Isak (4 pts)</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>8</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H32" t="n">
         <v>31</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>© Isak (4 pts)</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>8</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -5169,24 +4805,24 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>© B.Fernandes (4 pts)</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>3</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H33" t="n">
         <v>30</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>© B.Fernandes (4 pts)</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>3</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -5216,24 +4852,24 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>© João Pedro (0 pts)</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
-        <v>-1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H34" t="n">
         <v>30</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>© João Pedro (0 pts)</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>-1</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -5263,24 +4899,24 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>© Haaland (4 pts)</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
-        <v>11</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H35" t="n">
         <v>29</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>© Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>11</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -5310,24 +4946,24 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>© B.Fernandes (4 pts)</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
-        <v>7</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H36" t="n">
         <v>29</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>© B.Fernandes (4 pts)</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>7</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5357,24 +4993,24 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>© Semenyo (4 pts)</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
-        <v>14</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H37" t="n">
         <v>28</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>© Semenyo (4 pts)</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>14</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5404,24 +5040,24 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>© Haaland (4 pts)</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>7</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H38" t="n">
         <v>28</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>© Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>7</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5451,24 +5087,24 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>© Isak (4 pts)</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>2</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H39" t="n">
         <v>28</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>© Isak (4 pts)</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>2</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5498,24 +5134,24 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>© Anderson (4 pts)</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H40" t="n">
         <v>28</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>© Anderson (4 pts)</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>1</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5545,24 +5181,24 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>© Haaland (4 pts)</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
-        <v>10</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H41" t="n">
         <v>26</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>© Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>10</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5592,24 +5228,24 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>© B.Fernandes (4 pts)</t>
-        </is>
-      </c>
-      <c r="G42" t="n">
-        <v>11</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H42" t="n">
         <v>25</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>© B.Fernandes (4 pts)</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>11</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5639,24 +5275,24 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>© B.Fernandes (4 pts)</t>
-        </is>
-      </c>
-      <c r="G43" t="n">
-        <v>3</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H43" t="n">
         <v>25</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>© B.Fernandes (4 pts)</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>3</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -5686,24 +5322,24 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>© B.Fernandes (4 pts)</t>
-        </is>
-      </c>
-      <c r="G44" t="n">
-        <v>8</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H44" t="n">
         <v>20</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>© B.Fernandes (4 pts)</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>8</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -5733,24 +5369,24 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>© Haaland (4 pts)</t>
-        </is>
-      </c>
-      <c r="G45" t="n">
-        <v>9</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H45" t="n">
         <v>12</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>© Haaland (4 pts)</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>9</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -6526,12 +6162,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sittinon's Team</t>
+          <t>Wat Nong+ Pla NiL FC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sittinon Temsongsai</t>
+          <t>Piyabut Promrungruang</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -6592,12 +6228,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Wat Nong+ Pla NiL FC</t>
+          <t>Sittinon's Team</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Piyabut Promrungruang</t>
+          <t>Sittinon Temsongsai</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -6658,12 +6294,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lek C King</t>
+          <t>RiceCooker</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Banyawake Tharnthong</t>
+          <t>Chaiwat Munkong</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -6724,12 +6360,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RiceCooker</t>
+          <t>PheT9</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chaiwat Munkong</t>
+          <t>Phachara Wannarat</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -6790,12 +6426,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PheT9</t>
+          <t>Lek C King</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Phachara Wannarat</t>
+          <t>Banyawake Tharnthong</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -6922,12 +6558,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ทีมของ Kritsada</t>
+          <t>Yenzo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kritsada saejueng</t>
+          <t>Xabi Alonso</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -6988,12 +6624,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Yenzo</t>
+          <t>Aofmook Fc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Xabi Alonso</t>
+          <t>Tuntawat Juntun</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -7054,12 +6690,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Aofmook Fc</t>
+          <t>ทีมของ Kritsada</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tuntawat Juntun</t>
+          <t>Kritsada saejueng</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -7252,12 +6888,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tengen El Paso</t>
+          <t>ผู้บ่าวไทบ้าน</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>EL Paso slow-bar Coffee</t>
+          <t>Thanit Sophajit</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -7318,12 +6954,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ผู้บ่าวไทบ้าน</t>
+          <t>Tengen El Paso</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Thanit Sophajit</t>
+          <t>EL Paso slow-bar Coffee</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -7648,12 +7284,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Winning Standard FC</t>
+          <t>N. DE JOE</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Maytapat Yurawattarapon</t>
+          <t>Nawapon Dechabun</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -7714,12 +7350,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>N. DE JOE</t>
+          <t>Winning Standard FC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nawapon Dechabun</t>
+          <t>Maytapat Yurawattarapon</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -7780,12 +7416,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Pending Moderation</t>
+          <t>Aruch's Team</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pongsit Srisorn</t>
+          <t>Aruch Changthong</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -7846,12 +7482,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Aruch's Team</t>
+          <t>Pending Moderation</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Aruch Changthong</t>
+          <t>Pongsit Srisorn</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -7912,12 +7548,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PS</t>
+          <t>eakachai@romeO</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Pongnarin Savangvong</t>
+          <t>Eakachai Hamhomvong</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -7978,12 +7614,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>eakachai@romeO</t>
+          <t>PS</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Eakachai Hamhomvong</t>
+          <t>Pongnarin Savangvong</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -8044,12 +7680,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>KingPro</t>
+          <t>อนุบาลห้วยทับทัน</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>จิรวัฒน์ ขนอม</t>
+          <t>Chinnaarch Thanapongphasin</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -8110,12 +7746,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>อนุบาลห้วยทับทัน</t>
+          <t>KingPro</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chinnaarch Thanapongphasin</t>
+          <t>จิรวัฒน์ ขนอม</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -8242,12 +7878,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>US TM</t>
+          <t>Pending Moderation</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>rawat rummamai</t>
+          <t>Sukit Mattanaweerapong</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -8308,12 +7944,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Pending Moderation</t>
+          <t>Wayuchocolate</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sukit Mattanaweerapong</t>
+          <t>Ponlakit Choeychang</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -8374,12 +8010,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Wayuchocolate</t>
+          <t>US TM</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ponlakit Choeychang</t>
+          <t>rawat rummamai</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -8506,12 +8142,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Okaynaja</t>
+          <t>C-KING</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sir Okaynaja</t>
+          <t>Theera Tiawilai</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -8572,12 +8208,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>C-KING</t>
+          <t>Okaynaja</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Theera Tiawilai</t>
+          <t>Sir Okaynaja</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -9141,12 +8777,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sittinon's Team</t>
+          <t>Wat Nong+ Pla NiL FC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sittinon Temsongsai</t>
+          <t>Piyabut Promrungruang</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -9173,12 +8809,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Wat Nong+ Pla NiL FC</t>
+          <t>Sittinon's Team</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Piyabut Promrungruang</t>
+          <t>Sittinon Temsongsai</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -9205,12 +8841,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Lek C King</t>
+          <t>RiceCooker</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Banyawake Tharnthong</t>
+          <t>Chaiwat Munkong</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -9237,12 +8873,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RiceCooker</t>
+          <t>PheT9</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Chaiwat Munkong</t>
+          <t>Phachara Wannarat</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -9257,7 +8893,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GW1</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -9269,12 +8905,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PheT9</t>
+          <t>Lek C King</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Phachara Wannarat</t>
+          <t>Banyawake Tharnthong</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -9289,7 +8925,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>GW1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -9333,12 +8969,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ทีมของ Kritsada</t>
+          <t>Yenzo</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Kritsada saejueng</t>
+          <t>Xabi Alonso</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -9365,12 +9001,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Yenzo</t>
+          <t>Aofmook Fc</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Xabi Alonso</t>
+          <t>Tuntawat Juntun</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -9397,12 +9033,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Aofmook Fc</t>
+          <t>ทีมของ Kritsada</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tuntawat Juntun</t>
+          <t>Kritsada saejueng</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -9493,12 +9129,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Tengen El Paso</t>
+          <t>ผู้บ่าวไทบ้าน</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>EL Paso slow-bar Coffee</t>
+          <t>Thanit Sophajit</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -9525,12 +9161,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ผู้บ่าวไทบ้าน</t>
+          <t>Tengen El Paso</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Thanit Sophajit</t>
+          <t>EL Paso slow-bar Coffee</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -9685,12 +9321,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Winning Standard FC</t>
+          <t>N. DE JOE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Maytapat Yurawattarapon</t>
+          <t>Nawapon Dechabun</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -9717,12 +9353,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>N. DE JOE</t>
+          <t>Winning Standard FC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nawapon Dechabun</t>
+          <t>Maytapat Yurawattarapon</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -9749,12 +9385,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Pending Moderation</t>
+          <t>Aruch's Team</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Pongsit Srisorn</t>
+          <t>Aruch Changthong</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -9781,12 +9417,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Aruch's Team</t>
+          <t>Pending Moderation</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Aruch Changthong</t>
+          <t>Pongsit Srisorn</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -9813,12 +9449,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PS</t>
+          <t>eakachai@romeO</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Pongnarin Savangvong</t>
+          <t>Eakachai Hamhomvong</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -9845,12 +9481,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>eakachai@romeO</t>
+          <t>PS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Eakachai Hamhomvong</t>
+          <t>Pongnarin Savangvong</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -9877,12 +9513,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>KingPro</t>
+          <t>อนุบาลห้วยทับทัน</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>จิรวัฒน์ ขนอม</t>
+          <t>Chinnaarch Thanapongphasin</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -9909,12 +9545,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>อนุบาลห้วยทับทัน</t>
+          <t>KingPro</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Chinnaarch Thanapongphasin</t>
+          <t>จิรวัฒน์ ขนอม</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -9973,12 +9609,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>US TM</t>
+          <t>Pending Moderation</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>rawat rummamai</t>
+          <t>Sukit Mattanaweerapong</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -10005,12 +9641,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Pending Moderation</t>
+          <t>Wayuchocolate</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Sukit Mattanaweerapong</t>
+          <t>Ponlakit Choeychang</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -10037,12 +9673,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Wayuchocolate</t>
+          <t>US TM</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ponlakit Choeychang</t>
+          <t>rawat rummamai</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -10101,12 +9737,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Okaynaja</t>
+          <t>C-KING</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Sir Okaynaja</t>
+          <t>Theera Tiawilai</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -10133,12 +9769,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>C-KING</t>
+          <t>Okaynaja</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Theera Tiawilai</t>
+          <t>Sir Okaynaja</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">

--- a/FPL_League_506845_GW1_Full_Season.xlsx
+++ b/FPL_League_506845_GW1_Full_Season.xlsx
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nuttawut's Team</t>
+          <t>Klong 5 Rovers</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nuttawut Chutipong</t>
+          <t>Guy Klong5</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Klong 5 Rovers</t>
+          <t>Nuttawut's Team</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Guy Klong5</t>
+          <t>Nuttawut Chutipong</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1276,12 +1276,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Wat Nong+ Pla NiL FC</t>
+          <t>Sittinon's Team</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Piyabut Promrungruang</t>
+          <t>Sittinon Temsongsai</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sittinon's Team</t>
+          <t>Wat Nong+ Pla NiL FC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sittinon Temsongsai</t>
+          <t>Piyabut Promrungruang</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PheT9</t>
+          <t>Lek C King</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Phachara Wannarat</t>
+          <t>Banyawake Tharnthong</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1508,12 +1508,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lek C King</t>
+          <t>PheT9</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Banyawake Tharnthong</t>
+          <t>Phachara Wannarat</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DATE26th</t>
+          <t>Aofmook Fc</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Prarunya Kamahayung</t>
+          <t>Tuntawat Juntun</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Yenzo</t>
+          <t>ทีมของ Kritsada</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Xabi Alonso</t>
+          <t>Kritsada saejueng</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1682,12 +1682,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Aofmook Fc</t>
+          <t>Yenzo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tuntawat Juntun</t>
+          <t>Xabi Alonso</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ทีมของ Kritsada</t>
+          <t>DATE26th</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kritsada saejueng</t>
+          <t>Prarunya Kamahayung</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1856,12 +1856,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pimson Team</t>
+          <t>ผู้บ่าวไทบ้าน</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chanwit Pimson</t>
+          <t>Thanit Sophajit</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ผู้บ่าวไทบ้าน</t>
+          <t>Pimson Team</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Thanit Sophajit</t>
+          <t>Chanwit Pimson</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>รถซื้อแกง จะแรงได้ไง</t>
+          <t>N. DE JOE</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nuttapong Limadisai</t>
+          <t>Nawapon Dechabun</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>N. DE JOE</t>
+          <t>รถซื้อแกง จะแรงได้ไง</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nawapon Dechabun</t>
+          <t>Nuttapong Limadisai</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -2378,12 +2378,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Aruch's Team</t>
+          <t>Pending Moderation</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Aruch Changthong</t>
+          <t>Pongsit Srisorn</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -2436,12 +2436,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Pending Moderation</t>
+          <t>Aruch's Team</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pongsit Srisorn</t>
+          <t>Aruch Changthong</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>อนุบาลห้วยทับทัน</t>
+          <t>KingPro</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chinnaarch Thanapongphasin</t>
+          <t>จิรวัฒน์ ขนอม</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -2668,12 +2668,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>KingPro</t>
+          <t>อนุบาลห้วยทับทัน</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>จิรวัฒน์ ขนอม</t>
+          <t>Chinnaarch Thanapongphasin</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -2726,12 +2726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Marcomon FC</t>
+          <t>Pending Moderation</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Montri Chamchuklin</t>
+          <t>Sukit Mattanaweerapong</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -2784,12 +2784,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Pending Moderation</t>
+          <t>US TM</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sukit Mattanaweerapong</t>
+          <t>rawat rummamai</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>US TM</t>
+          <t>Marcomon FC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>rawat rummamai</t>
+          <t>Montri Chamchuklin</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -3016,12 +3016,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>C-KING</t>
+          <t>Okaynaja</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Theera Tiawilai</t>
+          <t>Sir Okaynaja</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Okaynaja</t>
+          <t>C-KING</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sir Okaynaja</t>
+          <t>Theera Tiawilai</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nuttawut's Team</t>
+          <t>Klong 5 Rovers</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nuttawut Chutipong</t>
+          <t>Guy Klong5</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -5964,12 +5964,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Klong 5 Rovers</t>
+          <t>Nuttawut's Team</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Guy Klong5</t>
+          <t>Nuttawut Chutipong</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Wat Nong+ Pla NiL FC</t>
+          <t>Sittinon's Team</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Piyabut Promrungruang</t>
+          <t>Sittinon Temsongsai</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sittinon's Team</t>
+          <t>Wat Nong+ Pla NiL FC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sittinon Temsongsai</t>
+          <t>Piyabut Promrungruang</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PheT9</t>
+          <t>Lek C King</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Phachara Wannarat</t>
+          <t>Banyawake Tharnthong</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lek C King</t>
+          <t>PheT9</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Banyawake Tharnthong</t>
+          <t>Phachara Wannarat</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DATE26th</t>
+          <t>Aofmook Fc</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Prarunya Kamahayung</t>
+          <t>Tuntawat Juntun</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -6558,12 +6558,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Yenzo</t>
+          <t>ทีมของ Kritsada</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Xabi Alonso</t>
+          <t>Kritsada saejueng</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Aofmook Fc</t>
+          <t>Yenzo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tuntawat Juntun</t>
+          <t>Xabi Alonso</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ทีมของ Kritsada</t>
+          <t>DATE26th</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kritsada saejueng</t>
+          <t>Prarunya Kamahayung</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -6822,12 +6822,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pimson Team</t>
+          <t>ผู้บ่าวไทบ้าน</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chanwit Pimson</t>
+          <t>Thanit Sophajit</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ผู้บ่าวไทบ้าน</t>
+          <t>Pimson Team</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Thanit Sophajit</t>
+          <t>Chanwit Pimson</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -7218,12 +7218,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>รถซื้อแกง จะแรงได้ไง</t>
+          <t>N. DE JOE</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nuttapong Limadisai</t>
+          <t>Nawapon Dechabun</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -7284,12 +7284,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>N. DE JOE</t>
+          <t>รถซื้อแกง จะแรงได้ไง</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nawapon Dechabun</t>
+          <t>Nuttapong Limadisai</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Aruch's Team</t>
+          <t>Pending Moderation</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Aruch Changthong</t>
+          <t>Pongsit Srisorn</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Pending Moderation</t>
+          <t>Aruch's Team</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pongsit Srisorn</t>
+          <t>Aruch Changthong</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -7680,12 +7680,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>อนุบาลห้วยทับทัน</t>
+          <t>KingPro</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chinnaarch Thanapongphasin</t>
+          <t>จิรวัฒน์ ขนอม</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -7746,12 +7746,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>KingPro</t>
+          <t>อนุบาลห้วยทับทัน</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>จิรวัฒน์ ขนอม</t>
+          <t>Chinnaarch Thanapongphasin</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -7812,12 +7812,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Marcomon FC</t>
+          <t>Pending Moderation</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Montri Chamchuklin</t>
+          <t>Sukit Mattanaweerapong</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Pending Moderation</t>
+          <t>US TM</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sukit Mattanaweerapong</t>
+          <t>rawat rummamai</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -8010,12 +8010,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>US TM</t>
+          <t>Marcomon FC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>rawat rummamai</t>
+          <t>Montri Chamchuklin</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>C-KING</t>
+          <t>Okaynaja</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Theera Tiawilai</t>
+          <t>Sir Okaynaja</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Okaynaja</t>
+          <t>C-KING</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sir Okaynaja</t>
+          <t>Theera Tiawilai</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -8649,12 +8649,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Nuttawut's Team</t>
+          <t>Klong 5 Rovers</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nuttawut Chutipong</t>
+          <t>Guy Klong5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -8681,12 +8681,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Klong 5 Rovers</t>
+          <t>Nuttawut's Team</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Guy Klong5</t>
+          <t>Nuttawut Chutipong</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -8777,12 +8777,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Wat Nong+ Pla NiL FC</t>
+          <t>Sittinon's Team</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Piyabut Promrungruang</t>
+          <t>Sittinon Temsongsai</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -8809,12 +8809,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sittinon's Team</t>
+          <t>Wat Nong+ Pla NiL FC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sittinon Temsongsai</t>
+          <t>Piyabut Promrungruang</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -8873,12 +8873,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PheT9</t>
+          <t>Lek C King</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Phachara Wannarat</t>
+          <t>Banyawake Tharnthong</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -8893,7 +8893,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>GW1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -8905,12 +8905,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Lek C King</t>
+          <t>PheT9</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Banyawake Tharnthong</t>
+          <t>Phachara Wannarat</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -8925,7 +8925,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GW1</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -8937,12 +8937,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DATE26th</t>
+          <t>Aofmook Fc</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Prarunya Kamahayung</t>
+          <t>Tuntawat Juntun</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -8969,12 +8969,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Yenzo</t>
+          <t>ทีมของ Kritsada</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Xabi Alonso</t>
+          <t>Kritsada saejueng</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -9001,12 +9001,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Aofmook Fc</t>
+          <t>Yenzo</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tuntawat Juntun</t>
+          <t>Xabi Alonso</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -9033,12 +9033,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ทีมของ Kritsada</t>
+          <t>DATE26th</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Kritsada saejueng</t>
+          <t>Prarunya Kamahayung</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -9097,12 +9097,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Pimson Team</t>
+          <t>ผู้บ่าวไทบ้าน</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Chanwit Pimson</t>
+          <t>Thanit Sophajit</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -9129,12 +9129,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ผู้บ่าวไทบ้าน</t>
+          <t>Pimson Team</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Thanit Sophajit</t>
+          <t>Chanwit Pimson</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -9289,12 +9289,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>รถซื้อแกง จะแรงได้ไง</t>
+          <t>N. DE JOE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nuttapong Limadisai</t>
+          <t>Nawapon Dechabun</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -9321,12 +9321,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>N. DE JOE</t>
+          <t>รถซื้อแกง จะแรงได้ไง</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nawapon Dechabun</t>
+          <t>Nuttapong Limadisai</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -9385,12 +9385,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Aruch's Team</t>
+          <t>Pending Moderation</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Aruch Changthong</t>
+          <t>Pongsit Srisorn</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -9417,12 +9417,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Pending Moderation</t>
+          <t>Aruch's Team</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Pongsit Srisorn</t>
+          <t>Aruch Changthong</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -9513,12 +9513,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>อนุบาลห้วยทับทัน</t>
+          <t>KingPro</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Chinnaarch Thanapongphasin</t>
+          <t>จิรวัฒน์ ขนอม</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -9545,12 +9545,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>KingPro</t>
+          <t>อนุบาลห้วยทับทัน</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>จิรวัฒน์ ขนอม</t>
+          <t>Chinnaarch Thanapongphasin</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -9577,12 +9577,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Marcomon FC</t>
+          <t>Pending Moderation</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Montri Chamchuklin</t>
+          <t>Sukit Mattanaweerapong</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -9609,12 +9609,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Pending Moderation</t>
+          <t>US TM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sukit Mattanaweerapong</t>
+          <t>rawat rummamai</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -9673,12 +9673,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>US TM</t>
+          <t>Marcomon FC</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>rawat rummamai</t>
+          <t>Montri Chamchuklin</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -9737,12 +9737,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>C-KING</t>
+          <t>Okaynaja</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Theera Tiawilai</t>
+          <t>Sir Okaynaja</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -9769,12 +9769,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Okaynaja</t>
+          <t>C-KING</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Sir Okaynaja</t>
+          <t>Theera Tiawilai</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">

--- a/FPL_League_506845_GW1_Full_Season.xlsx
+++ b/FPL_League_506845_GW1_Full_Season.xlsx
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="E2" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="E3" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
@@ -812,19 +812,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pending Moderation</t>
+          <t>Klong 5 Rovers</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Piyanat Cherdchoo</t>
+          <t>Guy Klong5</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E4" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
@@ -870,19 +870,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>APHICHAI  FC</t>
+          <t>PS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Aphichai Chanasook</t>
+          <t>Pongnarin Savangvong</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="E5" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
@@ -928,19 +928,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IS_AK 18</t>
+          <t>sirxpxk_</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>อิทธิวัฒน์ คำภา</t>
+          <t>sirxpxk _</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="E6" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
@@ -986,19 +986,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>sirxpxk_</t>
+          <t>IS_AK 18</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sirxpxk _</t>
+          <t>อิทธิวัฒน์ คำภา</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="E7" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
@@ -1044,19 +1044,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Klong 5 Rovers</t>
+          <t>7-a-side</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Guy Klong5</t>
+          <t>Punlert Ruttana</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E8" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
@@ -1102,19 +1102,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nuttawut's Team</t>
+          <t>Sittinon's Team</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Nuttawut Chutipong</t>
+          <t>Sittinon Temsongsai</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E9" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
@@ -1169,10 +1169,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="E10" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
@@ -1218,19 +1218,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Al-Nuser</t>
+          <t>RiceCooker</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Witsanu Munfak</t>
+          <t>Chaiwat Munkong</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E11" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
@@ -1276,19 +1276,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sittinon's Team</t>
+          <t>Pending Moderation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sittinon Temsongsai</t>
+          <t>Piyanat Cherdchoo</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E12" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -1334,19 +1334,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Wat Nong+ Pla NiL FC</t>
+          <t>PheT9</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Piyabut Promrungruang</t>
+          <t>Phachara Wannarat</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E13" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
@@ -1392,19 +1392,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RiceCooker</t>
+          <t>Al-Nuser</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chaiwat Munkong</t>
+          <t>Witsanu Munfak</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="E14" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
@@ -1450,19 +1450,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lek C King</t>
+          <t>อนุบาลห้วยทับทัน</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Banyawake Tharnthong</t>
+          <t>Chinnaarch Thanapongphasin</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="E15" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
@@ -1508,19 +1508,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PheT9</t>
+          <t>APHICHAI  FC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Phachara Wannarat</t>
+          <t>Aphichai Chanasook</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
@@ -1566,19 +1566,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Aofmook Fc</t>
+          <t>รถซื้อแกง จะแรงได้ไง</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tuntawat Juntun</t>
+          <t>Nuttapong Limadisai</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E17" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
@@ -1624,19 +1624,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ทีมของ Kritsada</t>
+          <t>Lek C King</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kritsada saejueng</t>
+          <t>Banyawake Tharnthong</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E18" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
@@ -1682,19 +1682,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Yenzo</t>
+          <t>N. DE JOE</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Xabi Alonso</t>
+          <t>Nawapon Dechabun</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E19" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
@@ -1740,19 +1740,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DATE26th</t>
+          <t>Aofmook Fc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Prarunya Kamahayung</t>
+          <t>Tuntawat Juntun</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="E20" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
@@ -1798,19 +1798,19 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JK Blookner Olivera</t>
+          <t>Yenzo</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tanawut Polchamni</t>
+          <t>Xabi Alonso</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="E21" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
@@ -1856,19 +1856,19 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ผู้บ่าวไทบ้าน</t>
+          <t>ทีมของ Kritsada</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Thanit Sophajit</t>
+          <t>Kritsada saejueng</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="E22" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
@@ -1914,19 +1914,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pimson Team</t>
+          <t>Nuttawut's Team</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chanwit Pimson</t>
+          <t>Nuttawut Chutipong</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="E23" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
@@ -1972,19 +1972,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tengen El Paso</t>
+          <t>C-KING</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>EL Paso slow-bar Coffee</t>
+          <t>Theera Tiawilai</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="E24" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
@@ -2030,19 +2030,19 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>7-a-side</t>
+          <t>Pimson Team</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Punlert Ruttana</t>
+          <t>Chanwit Pimson</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="E25" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
@@ -2088,19 +2088,19 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Raminthra Classic FC</t>
+          <t>ผู้บ่าวไทบ้าน</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chaichana Pathomekmongkhon</t>
+          <t>Thanit Sophajit</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="E26" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
@@ -2146,19 +2146,19 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>onelove2499</t>
+          <t>Tengen El Paso</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mongkhol Namsang</t>
+          <t>EL Paso slow-bar Coffee</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="E27" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
@@ -2204,19 +2204,19 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>N. DE JOE</t>
+          <t>Wat Nong+ Pla NiL FC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nawapon Dechabun</t>
+          <t>Piyabut Promrungruang</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E28" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
@@ -2262,19 +2262,19 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>รถซื้อแกง จะแรงได้ไง</t>
+          <t>Winning Standard FC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nuttapong Limadisai</t>
+          <t>Maytapat Yurawattarapon</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="E29" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
@@ -2320,19 +2320,19 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Winning Standard FC</t>
+          <t>eakachai@romeO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Maytapat Yurawattarapon</t>
+          <t>Eakachai Hamhomvong</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E30" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
@@ -2378,19 +2378,19 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Pending Moderation</t>
+          <t>KingPro</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pongsit Srisorn</t>
+          <t>จิรวัฒน์ ขนอม</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E31" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
@@ -2436,19 +2436,19 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Aruch's Team</t>
+          <t>DATE26th</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Aruch Changthong</t>
+          <t>Prarunya Kamahayung</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="E32" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
@@ -2494,19 +2494,19 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>eakachai@romeO</t>
+          <t>Marcomon FC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Eakachai Hamhomvong</t>
+          <t>Montri Chamchuklin</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E33" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
@@ -2552,19 +2552,19 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PS</t>
+          <t>Aruch's Team</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pongnarin Savangvong</t>
+          <t>Aruch Changthong</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E34" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
@@ -2610,19 +2610,19 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>KingPro</t>
+          <t>Wayuchocolate</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>จิรวัฒน์ ขนอม</t>
+          <t>Ponlakit Choeychang</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="E35" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
@@ -2668,19 +2668,19 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>อนุบาลห้วยทับทัน</t>
+          <t>JK Blookner Olivera</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chinnaarch Thanapongphasin</t>
+          <t>Tanawut Polchamni</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E36" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
@@ -2726,19 +2726,19 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Pending Moderation</t>
+          <t>Notta</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sukit Mattanaweerapong</t>
+          <t>Jirawat Ritnamkham</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="E37" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
@@ -2784,19 +2784,19 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>US TM</t>
+          <t>Okaynaja</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>rawat rummamai</t>
+          <t>Sir Okaynaja</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E38" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
@@ -2842,19 +2842,19 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Wayuchocolate</t>
+          <t>onelove2499</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ponlakit Choeychang</t>
+          <t>Mongkhol Namsang</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E39" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
@@ -2900,19 +2900,19 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Marcomon FC</t>
+          <t>Raminthra Classic FC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Montri Chamchuklin</t>
+          <t>Chaichana Pathomekmongkhon</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E40" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
@@ -2958,19 +2958,19 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Notta</t>
+          <t>Pending Moderation</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jirawat Ritnamkham</t>
+          <t>Pongsit Srisorn</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E41" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
@@ -3016,19 +3016,19 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Okaynaja</t>
+          <t>US TM</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sir Okaynaja</t>
+          <t>rawat rummamai</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E42" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
@@ -3074,19 +3074,19 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>C-KING</t>
+          <t>Pending Moderation</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Theera Tiawilai</t>
+          <t>Sukit Mattanaweerapong</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E43" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
@@ -3199,10 +3199,10 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E45" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
@@ -3266,7 +3266,7 @@
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="82" customWidth="1" min="11" max="11"/>
+    <col width="83" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3331,20 +3331,20 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>APHICHAI  FC</t>
+          <t>Klong 5 Rovers</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Aphichai Chanasook</t>
+          <t>Guy Klong5</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3357,15 +3357,15 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>© Mbeumo (4 pts)</t>
+          <t>© Haaland (4 pts)</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -3378,20 +3378,20 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Nuttawut's Team</t>
+          <t>PS</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Nuttawut Chutipong</t>
+          <t>Pongnarin Savangvong</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3404,15 +3404,15 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>© Saka (18 pts)</t>
+          <t>© João Pedro (22 pts)</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -3425,20 +3425,20 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Klong 5 Rovers</t>
+          <t>sirxpxk_</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Guy Klong5</t>
+          <t>sirxpxk _</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -3451,19 +3451,19 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>© Haaland (4 pts)</t>
+          <t>© Rogers (16 pts)</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>แพ้ไทเบรกเกอร์กัปตัน (4 vs 18)</t>
+          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
         </is>
       </c>
     </row>
@@ -3472,20 +3472,20 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>sirxpxk_</t>
+          <t>7-a-side</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>sirxpxk _</t>
+          <t>Punlert Ruttana</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -3498,19 +3498,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>© Rogers (0 pts)</t>
+          <t>© Haaland (4 pts)</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>แพ้ไทเบรกเกอร์กัปตัน (0 vs 4)</t>
+          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
         </is>
       </c>
     </row>
@@ -3519,33 +3519,33 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dogor Dorgu</t>
+          <t>Untapan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Piyapong Hongsuwan</t>
+          <t>Pakpong L.</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Bench Boost (BB)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -3553,11 +3553,11 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
+          <t>ใช้ BB -&gt; หักสำรอง 4 คน [Kinsky(2), Kerkez(0), Xhaka(9), Bogle(6)]</t>
         </is>
       </c>
     </row>
@@ -3566,33 +3566,33 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Untapan</t>
+          <t>Dogor Dorgu</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Pakpong L.</t>
+          <t>Piyapong Hongsuwan</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bench Boost (BB)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -3600,11 +3600,11 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>ใช้ BB -&gt; หักสำรอง 4 คน [Kinsky(2), Kerkez(0), Xhaka(9), Bogle(6)]</t>
+          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
         </is>
       </c>
     </row>
@@ -3613,20 +3613,20 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Al-Nuser</t>
+          <t>Sittinon's Team</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Witsanu Munfak</t>
+          <t>Sittinon Temsongsai</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -3647,11 +3647,11 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
+          <t>แพ้ไทเบรกเกอร์สำรอง (7 vs 9)</t>
         </is>
       </c>
     </row>
@@ -3660,20 +3660,20 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wat Nong+ Pla NiL FC</t>
+          <t>RiceCooker</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Piyabut Promrungruang</t>
+          <t>Chaiwat Munkong</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -3686,15 +3686,15 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>© Haaland (4 pts)</t>
+          <t>© Gabriel (10 pts)</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -3707,20 +3707,20 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sittinon's Team</t>
+          <t>Al-Nuser</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sittinon Temsongsai</t>
+          <t>Witsanu Munfak</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -3741,11 +3741,11 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>แพ้ไทเบรกเกอร์สำรอง (7 vs 12)</t>
+          <t>แพ้ไทเบรกเกอร์กัปตัน (4 vs 10)</t>
         </is>
       </c>
     </row>
@@ -3754,45 +3754,45 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>IS_AK 18</t>
+          <t>อนุบาลห้วยทับทัน</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>อิทธิวัฒน์ คำภา</t>
+          <t>Chinnaarch Thanapongphasin</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bench Boost (BB)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>© Haaland (4 pts)</t>
+          <t>© B.Fernandes (4 pts)</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>แพ้ไทเบรกเกอร์สำรอง (6 vs 7)</t>
+          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
         </is>
       </c>
     </row>
@@ -3801,20 +3801,20 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>RiceCooker</t>
+          <t>APHICHAI  FC</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Chaiwat Munkong</t>
+          <t>Aphichai Chanasook</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -3827,15 +3827,15 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>© Gabriel (10 pts)</t>
+          <t>© Mbeumo (4 pts)</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -3882,11 +3882,11 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>แพ้ไทเบรกเกอร์กัปตัน (6 vs 10)</t>
+          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
         </is>
       </c>
     </row>
@@ -3899,16 +3899,16 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DATE26th</t>
+          <t>รถซื้อแกง จะแรงได้ไง</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Prarunya Kamahayung</t>
+          <t>Nuttapong Limadisai</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3921,19 +3921,19 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>© Saka (18 pts)</t>
+          <t>© Haaland (4 pts)</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
+          <t>แพ้ไทเบรกเกอร์กัปตัน (4 vs 6)</t>
         </is>
       </c>
     </row>
@@ -3946,16 +3946,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Aofmook Fc</t>
+          <t>N. DE JOE</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Tuntawat Juntun</t>
+          <t>Nawapon Dechabun</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3968,19 +3968,19 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>© Raya (12 pts)</t>
+          <t>© Haaland (4 pts)</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>แพ้ไทเบรกเกอร์กัปตัน (12 vs 18)</t>
+          <t>แพ้ไทเบรกเกอร์สำรอง (3 vs 15)</t>
         </is>
       </c>
     </row>
@@ -3989,20 +3989,20 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ทีมของ Kritsada</t>
+          <t>Aofmook Fc</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Kritsada saejueng</t>
+          <t>Tuntawat Juntun</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -4015,19 +4015,19 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>© B.Fernandes (4 pts)</t>
+          <t>© Raya (12 pts)</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>แพ้ไทเบรกเกอร์กัปตัน (4 vs 12)</t>
+          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
         </is>
       </c>
     </row>
@@ -4036,20 +4036,20 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Yenzo</t>
+          <t>ทีมของ Kritsada</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Xabi Alonso</t>
+          <t>Kritsada saejueng</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -4062,19 +4062,19 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>© Haaland (4 pts)</t>
+          <t>© B.Fernandes (4 pts)</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>แพ้ไทเบรกเกอร์สำรอง (10 vs 12)</t>
+          <t>แพ้ไทเบรกเกอร์กัปตัน (4 vs 12)</t>
         </is>
       </c>
     </row>
@@ -4083,33 +4083,33 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pending Moderation</t>
+          <t>Yenzo</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Piyanat Cherdchoo</t>
+          <t>Xabi Alonso</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bench Boost (BB)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -4117,11 +4117,11 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>ใช้ BB -&gt; หักสำรอง 4 คน [Pickford(7), Richards(3), Jensen(6), Isidor(1)]</t>
+          <t>แพ้ไทเบรกเกอร์สำรอง (10 vs 12)</t>
         </is>
       </c>
     </row>
@@ -4130,20 +4130,20 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>JK Blookner Olivera</t>
+          <t>Nuttawut's Team</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Tanawut Polchamni</t>
+          <t>Nuttawut Chutipong</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -4156,19 +4156,19 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>© O'Reilly (4 pts)</t>
+          <t>© Saka (18 pts)</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>แพ้ไทเบรกเกอร์สำรอง (5 vs 17)</t>
+          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
         </is>
       </c>
     </row>
@@ -4177,20 +4177,20 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ผู้บ่าวไทบ้าน</t>
+          <t>C-KING</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Thanit Sophajit</t>
+          <t>Theera Tiawilai</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4203,19 +4203,19 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>© Haaland (4 pts)</t>
+          <t>© B.Fernandes (4 pts)</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
+          <t>แพ้ไทเบรกเกอร์กัปตัน (4 vs 18)</t>
         </is>
       </c>
     </row>
@@ -4224,20 +4224,20 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tengen El Paso</t>
+          <t>ผู้บ่าวไทบ้าน</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EL Paso slow-bar Coffee</t>
+          <t>Thanit Sophajit</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -4258,11 +4258,11 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>แพ้ไทเบรกเกอร์สำรอง (25 vs 29)</t>
+          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
         </is>
       </c>
     </row>
@@ -4271,20 +4271,20 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pimson Team</t>
+          <t>Tengen El Paso</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Chanwit Pimson</t>
+          <t>EL Paso slow-bar Coffee</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -4305,11 +4305,11 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>แพ้ไทเบรกเกอร์สำรอง (6 vs 25)</t>
+          <t>แพ้ไทเบรกเกอร์สำรอง (25 vs 29)</t>
         </is>
       </c>
     </row>
@@ -4318,33 +4318,33 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>7-a-side</t>
+          <t>IS_AK 18</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Punlert Ruttana</t>
+          <t>อิทธิวัฒน์ คำภา</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Bench Boost (BB)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -4352,11 +4352,11 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
+          <t>แพ้ไทเบรกเกอร์สำรอง (17 vs 25)</t>
         </is>
       </c>
     </row>
@@ -4365,20 +4365,20 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Raminthra Classic FC</t>
+          <t>Pimson Team</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Chaichana Pathomekmongkhon</t>
+          <t>Chanwit Pimson</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4391,19 +4391,19 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>© Gyökeres (0 pts)</t>
+          <t>© Haaland (4 pts)</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
+          <t>แพ้ไทเบรกเกอร์สำรอง (6 vs 17)</t>
         </is>
       </c>
     </row>
@@ -4412,45 +4412,45 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TanateR</t>
+          <t>Wat Nong+ Pla NiL FC</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ธเนศ รุจิ</t>
+          <t>Piyabut Promrungruang</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bench Boost (BB)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>© B.Fernandes (4 pts)</t>
+          <t>© Haaland (4 pts)</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>ใช้ BB -&gt; หักสำรอง 4 คน [Verbruggen(6), João Pedro(0), Gakpo(12), Gvardiol(9)]</t>
+          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
         </is>
       </c>
     </row>
@@ -4459,20 +4459,20 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>onelove2499</t>
+          <t>Winning Standard FC</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Mongkhol Namsang</t>
+          <t>Maytapat Yurawattarapon</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4485,19 +4485,19 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>© Haaland (4 pts)</t>
+          <t>© B.Fernandes (4 pts)</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>แพ้ไทเบรกเกอร์สำรอง (18 vs 27)</t>
+          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
         </is>
       </c>
     </row>
@@ -4506,45 +4506,45 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>รถซื้อแกง จะแรงได้ไง</t>
+          <t>PheT9</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Nuttapong Limadisai</t>
+          <t>Phachara Wannarat</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Bench Boost (BB)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>© Haaland (4 pts)</t>
+          <t>© B.Fernandes (4 pts)</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
+          <t>ใช้ BB -&gt; หักสำรอง 4 คน [Lammens(1), Palestra(0), Davis(2), Ndiaye(9)]</t>
         </is>
       </c>
     </row>
@@ -4553,20 +4553,20 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Winning Standard FC</t>
+          <t>eakachai@romeO</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Maytapat Yurawattarapon</t>
+          <t>Eakachai Hamhomvong</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -4587,11 +4587,11 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>แพ้ไทเบรกเกอร์สำรอง (6 vs 15)</t>
+          <t>แพ้ไทเบรกเกอร์สำรอง (3 vs 12)</t>
         </is>
       </c>
     </row>
@@ -4600,20 +4600,20 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>N. DE JOE</t>
+          <t>KingPro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Nawapon Dechabun</t>
+          <t>จิรวัฒน์ ขนอม</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -4634,11 +4634,11 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>แพ้ไทเบรกเกอร์สำรอง (3 vs 6)</t>
+          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
         </is>
       </c>
     </row>
@@ -4647,20 +4647,20 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Aruch's Team</t>
+          <t>DATE26th</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Aruch Changthong</t>
+          <t>Prarunya Kamahayung</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4673,15 +4673,15 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>© Rice (6 pts)</t>
+          <t>© Saka (18 pts)</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -4694,45 +4694,45 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PheT9</t>
+          <t>Aruch's Team</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Phachara Wannarat</t>
+          <t>Aruch Changthong</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bench Boost (BB)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>© B.Fernandes (4 pts)</t>
+          <t>© Rice (6 pts)</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>แพ้ไทเบรกเกอร์กัปตัน (4 vs 6)</t>
+          <t>แพ้ไทเบรกเกอร์กัปตัน (6 vs 18)</t>
         </is>
       </c>
     </row>
@@ -4741,20 +4741,20 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pending Moderation</t>
+          <t>Marcomon FC</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Pongsit Srisorn</t>
+          <t>Montri Chamchuklin</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4767,19 +4767,19 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>© Isak (4 pts)</t>
+          <t>© Semenyo (4 pts)</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>แพ้ไทเบรกเกอร์สำรอง (8 vs 12)</t>
+          <t>แพ้ไทเบรกเกอร์กัปตัน (4 vs 6)</t>
         </is>
       </c>
     </row>
@@ -4788,20 +4788,20 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>eakachai@romeO</t>
+          <t>Wayuchocolate</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Eakachai Hamhomvong</t>
+          <t>Ponlakit Choeychang</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4814,19 +4814,19 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>© B.Fernandes (4 pts)</t>
+          <t>© Anderson (4 pts)</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
+          <t>แพ้ไทเบรกเกอร์สำรอง (1 vs 14)</t>
         </is>
       </c>
     </row>
@@ -4835,45 +4835,45 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>PS</t>
+          <t>Pending Moderation</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Pongnarin Savangvong</t>
+          <t>Piyanat Cherdchoo</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Bench Boost (BB)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>© João Pedro (0 pts)</t>
+          <t>© Haaland (4 pts)</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>แพ้ไทเบรกเกอร์กัปตัน (0 vs 4)</t>
+          <t>ใช้ BB -&gt; หักสำรอง 4 คน [Pickford(7), Richards(3), Jensen(6), Isidor(1)]</t>
         </is>
       </c>
     </row>
@@ -4882,20 +4882,20 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>KingPro</t>
+          <t>Notta</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>จิรวัฒน์ ขนอม</t>
+          <t>Jirawat Ritnamkham</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -4916,11 +4916,11 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
+          <t>แพ้ไทเบรกเกอร์สำรอง (12 vs 17)</t>
         </is>
       </c>
     </row>
@@ -4929,20 +4929,20 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>อนุบาลห้วยทับทัน</t>
+          <t>JK Blookner Olivera</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Chinnaarch Thanapongphasin</t>
+          <t>Tanawut Polchamni</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4955,19 +4955,19 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>© B.Fernandes (4 pts)</t>
+          <t>© O'Reilly (4 pts)</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>แพ้ไทเบรกเกอร์สำรอง (7 vs 11)</t>
+          <t>แพ้ไทเบรกเกอร์สำรอง (5 vs 12)</t>
         </is>
       </c>
     </row>
@@ -4976,21 +4976,21 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
+        <v>37</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Okaynaja</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Sir Okaynaja</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
         <v>36</v>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Marcomon FC</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Montri Chamchuklin</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>28</v>
-      </c>
       <c r="F37" t="inlineStr">
         <is>
           <t>-</t>
@@ -5002,15 +5002,15 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>© Semenyo (4 pts)</t>
+          <t>© B.Fernandes (4 pts)</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5023,45 +5023,45 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pending Moderation</t>
+          <t>TanateR</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Sukit Mattanaweerapong</t>
+          <t>ธเนศ รุจิ</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Bench Boost (BB)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-38</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>© Haaland (4 pts)</t>
+          <t>© B.Fernandes (4 pts)</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>แพ้ไทเบรกเกอร์สำรอง (7 vs 14)</t>
+          <t>ใช้ BB -&gt; หักสำรอง 4 คน [Verbruggen(6), João Pedro(11), Gakpo(12), Gvardiol(9)]</t>
         </is>
       </c>
     </row>
@@ -5070,20 +5070,20 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US TM</t>
+          <t>onelove2499</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>rawat rummamai</t>
+          <t>Mongkhol Namsang</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5096,19 +5096,19 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>© Isak (4 pts)</t>
+          <t>© Haaland (4 pts)</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>แพ้ไทเบรกเกอร์สำรอง (2 vs 7)</t>
+          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
         </is>
       </c>
     </row>
@@ -5117,20 +5117,20 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Wayuchocolate</t>
+          <t>Raminthra Classic FC</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ponlakit Choeychang</t>
+          <t>Chaichana Pathomekmongkhon</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5143,19 +5143,19 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>© Anderson (4 pts)</t>
+          <t>© Gyökeres (0 pts)</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>แพ้ไทเบรกเกอร์สำรอง (1 vs 2)</t>
+          <t>แพ้ไทเบรกเกอร์กัปตัน (0 vs 4)</t>
         </is>
       </c>
     </row>
@@ -5168,16 +5168,16 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Notta</t>
+          <t>Pending Moderation</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Jirawat Ritnamkham</t>
+          <t>Pongsit Srisorn</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5190,15 +5190,15 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>© Haaland (4 pts)</t>
+          <t>© Isak (4 pts)</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5215,16 +5215,16 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Okaynaja</t>
+          <t>Pending Moderation</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Sir Okaynaja</t>
+          <t>Sukit Mattanaweerapong</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5237,15 +5237,15 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>© B.Fernandes (4 pts)</t>
+          <t>© Haaland (4 pts)</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5262,16 +5262,16 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>C-KING</t>
+          <t>US TM</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Theera Tiawilai</t>
+          <t>rawat rummamai</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5284,19 +5284,19 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>© B.Fernandes (4 pts)</t>
+          <t>© Isak (4 pts)</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>แพ้ไทเบรกเกอร์สำรอง (3 vs 11)</t>
+          <t>แพ้ไทเบรกเกอร์สำรอง (2 vs 7)</t>
         </is>
       </c>
     </row>
@@ -5339,7 +5339,7 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -5511,10 +5511,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="E2" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5577,10 +5577,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="E3" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -5634,19 +5634,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pending Moderation</t>
+          <t>Klong 5 Rovers</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Piyanat Cherdchoo</t>
+          <t>Guy Klong5</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E4" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -5700,19 +5700,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>APHICHAI  FC</t>
+          <t>PS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Aphichai Chanasook</t>
+          <t>Pongnarin Savangvong</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="E5" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -5766,19 +5766,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IS_AK 18</t>
+          <t>sirxpxk_</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>อิทธิวัฒน์ คำภา</t>
+          <t>sirxpxk _</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="E6" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -5832,19 +5832,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>sirxpxk_</t>
+          <t>IS_AK 18</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sirxpxk _</t>
+          <t>อิทธิวัฒน์ คำภา</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="E7" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -5898,19 +5898,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Klong 5 Rovers</t>
+          <t>7-a-side</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Guy Klong5</t>
+          <t>Punlert Ruttana</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E8" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -5964,19 +5964,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nuttawut's Team</t>
+          <t>Sittinon's Team</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Nuttawut Chutipong</t>
+          <t>Sittinon Temsongsai</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E9" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="E10" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -6096,19 +6096,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Al-Nuser</t>
+          <t>RiceCooker</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Witsanu Munfak</t>
+          <t>Chaiwat Munkong</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E11" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -6162,19 +6162,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sittinon's Team</t>
+          <t>Pending Moderation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sittinon Temsongsai</t>
+          <t>Piyanat Cherdchoo</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E12" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -6228,19 +6228,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Wat Nong+ Pla NiL FC</t>
+          <t>PheT9</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Piyabut Promrungruang</t>
+          <t>Phachara Wannarat</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E13" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -6294,19 +6294,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RiceCooker</t>
+          <t>Al-Nuser</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chaiwat Munkong</t>
+          <t>Witsanu Munfak</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="E14" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -6360,19 +6360,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lek C King</t>
+          <t>อนุบาลห้วยทับทัน</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Banyawake Tharnthong</t>
+          <t>Chinnaarch Thanapongphasin</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="E15" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -6426,19 +6426,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PheT9</t>
+          <t>APHICHAI  FC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Phachara Wannarat</t>
+          <t>Aphichai Chanasook</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -6492,19 +6492,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Aofmook Fc</t>
+          <t>รถซื้อแกง จะแรงได้ไง</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tuntawat Juntun</t>
+          <t>Nuttapong Limadisai</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E17" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -6558,19 +6558,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ทีมของ Kritsada</t>
+          <t>Lek C King</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kritsada saejueng</t>
+          <t>Banyawake Tharnthong</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E18" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -6624,19 +6624,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Yenzo</t>
+          <t>N. DE JOE</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Xabi Alonso</t>
+          <t>Nawapon Dechabun</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E19" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -6690,19 +6690,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DATE26th</t>
+          <t>Aofmook Fc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Prarunya Kamahayung</t>
+          <t>Tuntawat Juntun</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="E20" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -6756,19 +6756,19 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JK Blookner Olivera</t>
+          <t>Yenzo</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tanawut Polchamni</t>
+          <t>Xabi Alonso</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="E21" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -6822,19 +6822,19 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ผู้บ่าวไทบ้าน</t>
+          <t>ทีมของ Kritsada</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Thanit Sophajit</t>
+          <t>Kritsada saejueng</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="E22" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -6888,19 +6888,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pimson Team</t>
+          <t>Nuttawut's Team</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chanwit Pimson</t>
+          <t>Nuttawut Chutipong</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="E23" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -6954,19 +6954,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tengen El Paso</t>
+          <t>C-KING</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>EL Paso slow-bar Coffee</t>
+          <t>Theera Tiawilai</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="E24" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -7020,19 +7020,19 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>7-a-side</t>
+          <t>Pimson Team</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Punlert Ruttana</t>
+          <t>Chanwit Pimson</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="E25" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -7086,19 +7086,19 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Raminthra Classic FC</t>
+          <t>ผู้บ่าวไทบ้าน</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chaichana Pathomekmongkhon</t>
+          <t>Thanit Sophajit</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="E26" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -7152,19 +7152,19 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>onelove2499</t>
+          <t>Tengen El Paso</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mongkhol Namsang</t>
+          <t>EL Paso slow-bar Coffee</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="E27" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -7218,19 +7218,19 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>N. DE JOE</t>
+          <t>Wat Nong+ Pla NiL FC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nawapon Dechabun</t>
+          <t>Piyabut Promrungruang</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E28" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -7284,19 +7284,19 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>รถซื้อแกง จะแรงได้ไง</t>
+          <t>Winning Standard FC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nuttapong Limadisai</t>
+          <t>Maytapat Yurawattarapon</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="E29" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -7350,19 +7350,19 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Winning Standard FC</t>
+          <t>eakachai@romeO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Maytapat Yurawattarapon</t>
+          <t>Eakachai Hamhomvong</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E30" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -7416,19 +7416,19 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Pending Moderation</t>
+          <t>KingPro</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pongsit Srisorn</t>
+          <t>จิรวัฒน์ ขนอม</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E31" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -7482,19 +7482,19 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Aruch's Team</t>
+          <t>DATE26th</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Aruch Changthong</t>
+          <t>Prarunya Kamahayung</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="E32" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -7548,19 +7548,19 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>eakachai@romeO</t>
+          <t>Marcomon FC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Eakachai Hamhomvong</t>
+          <t>Montri Chamchuklin</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E33" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -7614,19 +7614,19 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PS</t>
+          <t>Aruch's Team</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pongnarin Savangvong</t>
+          <t>Aruch Changthong</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E34" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -7680,19 +7680,19 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>KingPro</t>
+          <t>Wayuchocolate</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>จิรวัฒน์ ขนอม</t>
+          <t>Ponlakit Choeychang</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="E35" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -7746,19 +7746,19 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>อนุบาลห้วยทับทัน</t>
+          <t>JK Blookner Olivera</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chinnaarch Thanapongphasin</t>
+          <t>Tanawut Polchamni</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E36" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -7812,19 +7812,19 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Pending Moderation</t>
+          <t>Notta</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sukit Mattanaweerapong</t>
+          <t>Jirawat Ritnamkham</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="E37" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -7878,19 +7878,19 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>US TM</t>
+          <t>Okaynaja</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>rawat rummamai</t>
+          <t>Sir Okaynaja</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E38" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -7944,19 +7944,19 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Wayuchocolate</t>
+          <t>onelove2499</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ponlakit Choeychang</t>
+          <t>Mongkhol Namsang</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E39" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -8010,19 +8010,19 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Marcomon FC</t>
+          <t>Raminthra Classic FC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Montri Chamchuklin</t>
+          <t>Chaichana Pathomekmongkhon</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E40" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -8076,19 +8076,19 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Notta</t>
+          <t>Pending Moderation</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jirawat Ritnamkham</t>
+          <t>Pongsit Srisorn</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E41" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -8142,19 +8142,19 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Okaynaja</t>
+          <t>US TM</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sir Okaynaja</t>
+          <t>rawat rummamai</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E42" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -8208,19 +8208,19 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>C-KING</t>
+          <t>Pending Moderation</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Theera Tiawilai</t>
+          <t>Sukit Mattanaweerapong</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E43" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -8349,10 +8349,10 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E45" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -8521,12 +8521,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pending Moderation</t>
+          <t>Klong 5 Rovers</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Piyanat Cherdchoo</t>
+          <t>Guy Klong5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>GW1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -8553,12 +8553,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IS_AK 18</t>
+          <t>PS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>อิทธิวัฒน์ คำภา</t>
+          <t>Pongnarin Savangvong</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -8573,7 +8573,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>GW1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -8585,12 +8585,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>APHICHAI  FC</t>
+          <t>sirxpxk_</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Aphichai Chanasook</t>
+          <t>sirxpxk _</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -8617,12 +8617,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sirxpxk_</t>
+          <t>IS_AK 18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>sirxpxk _</t>
+          <t>อิทธิวัฒน์ คำภา</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GW1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -8649,12 +8649,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Klong 5 Rovers</t>
+          <t>7-a-side</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Guy Klong5</t>
+          <t>Punlert Ruttana</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -8681,12 +8681,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Nuttawut's Team</t>
+          <t>Sittinon's Team</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nuttawut Chutipong</t>
+          <t>Sittinon Temsongsai</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -8745,12 +8745,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Al-Nuser</t>
+          <t>RiceCooker</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Witsanu Munfak</t>
+          <t>Chaiwat Munkong</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -8777,12 +8777,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sittinon's Team</t>
+          <t>Pending Moderation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sittinon Temsongsai</t>
+          <t>Piyanat Cherdchoo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -8797,7 +8797,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GW1</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -8809,12 +8809,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Wat Nong+ Pla NiL FC</t>
+          <t>PheT9</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Piyabut Promrungruang</t>
+          <t>Phachara Wannarat</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -8829,7 +8829,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GW1</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -8841,12 +8841,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>RiceCooker</t>
+          <t>Al-Nuser</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Chaiwat Munkong</t>
+          <t>Witsanu Munfak</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -8873,12 +8873,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Lek C King</t>
+          <t>อนุบาลห้วยทับทัน</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Banyawake Tharnthong</t>
+          <t>Chinnaarch Thanapongphasin</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -8905,12 +8905,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PheT9</t>
+          <t>APHICHAI  FC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Phachara Wannarat</t>
+          <t>Aphichai Chanasook</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -8925,7 +8925,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>GW1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -8937,12 +8937,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Aofmook Fc</t>
+          <t>รถซื้อแกง จะแรงได้ไง</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tuntawat Juntun</t>
+          <t>Nuttapong Limadisai</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -8969,12 +8969,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ทีมของ Kritsada</t>
+          <t>Lek C King</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Kritsada saejueng</t>
+          <t>Banyawake Tharnthong</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -9001,12 +9001,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Yenzo</t>
+          <t>N. DE JOE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Xabi Alonso</t>
+          <t>Nawapon Dechabun</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -9033,12 +9033,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DATE26th</t>
+          <t>Aofmook Fc</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Prarunya Kamahayung</t>
+          <t>Tuntawat Juntun</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -9065,12 +9065,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>JK Blookner Olivera</t>
+          <t>Yenzo</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tanawut Polchamni</t>
+          <t>Xabi Alonso</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -9097,12 +9097,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ผู้บ่าวไทบ้าน</t>
+          <t>ทีมของ Kritsada</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Thanit Sophajit</t>
+          <t>Kritsada saejueng</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -9129,12 +9129,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Pimson Team</t>
+          <t>Nuttawut's Team</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Chanwit Pimson</t>
+          <t>Nuttawut Chutipong</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -9161,12 +9161,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Tengen El Paso</t>
+          <t>C-KING</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>EL Paso slow-bar Coffee</t>
+          <t>Theera Tiawilai</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -9193,12 +9193,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7-a-side</t>
+          <t>Pimson Team</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Punlert Ruttana</t>
+          <t>Chanwit Pimson</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -9225,12 +9225,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Raminthra Classic FC</t>
+          <t>ผู้บ่าวไทบ้าน</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Chaichana Pathomekmongkhon</t>
+          <t>Thanit Sophajit</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -9257,12 +9257,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>onelove2499</t>
+          <t>Tengen El Paso</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mongkhol Namsang</t>
+          <t>EL Paso slow-bar Coffee</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -9289,12 +9289,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>N. DE JOE</t>
+          <t>Wat Nong+ Pla NiL FC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nawapon Dechabun</t>
+          <t>Piyabut Promrungruang</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -9321,12 +9321,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>รถซื้อแกง จะแรงได้ไง</t>
+          <t>Winning Standard FC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nuttapong Limadisai</t>
+          <t>Maytapat Yurawattarapon</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -9353,12 +9353,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Winning Standard FC</t>
+          <t>eakachai@romeO</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Maytapat Yurawattarapon</t>
+          <t>Eakachai Hamhomvong</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -9385,12 +9385,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Pending Moderation</t>
+          <t>KingPro</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Pongsit Srisorn</t>
+          <t>จิรวัฒน์ ขนอม</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -9417,12 +9417,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Aruch's Team</t>
+          <t>DATE26th</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Aruch Changthong</t>
+          <t>Prarunya Kamahayung</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -9449,12 +9449,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>eakachai@romeO</t>
+          <t>Marcomon FC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Eakachai Hamhomvong</t>
+          <t>Montri Chamchuklin</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -9481,12 +9481,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PS</t>
+          <t>Aruch's Team</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Pongnarin Savangvong</t>
+          <t>Aruch Changthong</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -9513,12 +9513,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>KingPro</t>
+          <t>Wayuchocolate</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>จิรวัฒน์ ขนอม</t>
+          <t>Ponlakit Choeychang</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -9545,12 +9545,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>อนุบาลห้วยทับทัน</t>
+          <t>JK Blookner Olivera</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Chinnaarch Thanapongphasin</t>
+          <t>Tanawut Polchamni</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -9577,12 +9577,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Pending Moderation</t>
+          <t>Notta</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Sukit Mattanaweerapong</t>
+          <t>Jirawat Ritnamkham</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -9609,12 +9609,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>US TM</t>
+          <t>Okaynaja</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>rawat rummamai</t>
+          <t>Sir Okaynaja</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -9641,12 +9641,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Wayuchocolate</t>
+          <t>onelove2499</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ponlakit Choeychang</t>
+          <t>Mongkhol Namsang</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -9673,12 +9673,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Marcomon FC</t>
+          <t>Raminthra Classic FC</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Montri Chamchuklin</t>
+          <t>Chaichana Pathomekmongkhon</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -9705,12 +9705,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Notta</t>
+          <t>Pending Moderation</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Jirawat Ritnamkham</t>
+          <t>Pongsit Srisorn</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -9737,12 +9737,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Okaynaja</t>
+          <t>US TM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Sir Okaynaja</t>
+          <t>rawat rummamai</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -9769,12 +9769,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>C-KING</t>
+          <t>Pending Moderation</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Theera Tiawilai</t>
+          <t>Sukit Mattanaweerapong</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">

--- a/FPL_League_506845_GW1_Full_Season.xlsx
+++ b/FPL_League_506845_GW1_Full_Season.xlsx
@@ -1102,19 +1102,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sittinon's Team</t>
+          <t>Lek C King</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sittinon Temsongsai</t>
+          <t>Banyawake Tharnthong</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E9" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dogor Dorgu</t>
+          <t>Sittinon's Team</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Piyapong Hongsuwan</t>
+          <t>Sittinon Temsongsai</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1218,19 +1218,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RiceCooker</t>
+          <t>Dogor Dorgu</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chaiwat Munkong</t>
+          <t>Piyapong Hongsuwan</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E11" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
@@ -1276,12 +1276,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pending Moderation</t>
+          <t>Al-Nuser</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Piyanat Cherdchoo</t>
+          <t>Witsanu Munfak</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PheT9</t>
+          <t>Pending Moderation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Phachara Wannarat</t>
+          <t>Piyanat Cherdchoo</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Al-Nuser</t>
+          <t>PheT9</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Witsanu Munfak</t>
+          <t>Phachara Wannarat</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1450,19 +1450,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>อนุบาลห้วยทับทัน</t>
+          <t>RiceCooker</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chinnaarch Thanapongphasin</t>
+          <t>Chaiwat Munkong</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
@@ -1508,19 +1508,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>APHICHAI  FC</t>
+          <t>อนุบาลห้วยทับทัน</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Aphichai Chanasook</t>
+          <t>Chinnaarch Thanapongphasin</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E16" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
@@ -1566,19 +1566,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>รถซื้อแกง จะแรงได้ไง</t>
+          <t>Yenzo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nuttapong Limadisai</t>
+          <t>Xabi Alonso</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E17" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
@@ -1624,19 +1624,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lek C King</t>
+          <t>APHICHAI  FC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Banyawake Tharnthong</t>
+          <t>Aphichai Chanasook</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E18" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
@@ -1740,19 +1740,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Aofmook Fc</t>
+          <t>รถซื้อแกง จะแรงได้ไง</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tuntawat Juntun</t>
+          <t>Nuttapong Limadisai</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E20" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
@@ -1798,19 +1798,19 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Yenzo</t>
+          <t>Aofmook Fc</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Xabi Alonso</t>
+          <t>Tuntawat Juntun</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E21" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
@@ -1914,19 +1914,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nuttawut's Team</t>
+          <t>Pimson Team</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nuttawut Chutipong</t>
+          <t>Chanwit Pimson</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E23" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
@@ -2030,19 +2030,19 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Pimson Team</t>
+          <t>Nuttawut's Team</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chanwit Pimson</t>
+          <t>Nuttawut Chutipong</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E25" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
@@ -2088,19 +2088,19 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ผู้บ่าวไทบ้าน</t>
+          <t>Marcomon FC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Thanit Sophajit</t>
+          <t>Montri Chamchuklin</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E26" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
@@ -2146,12 +2146,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Tengen El Paso</t>
+          <t>Notta</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>EL Paso slow-bar Coffee</t>
+          <t>Jirawat Ritnamkham</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -2204,19 +2204,19 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Wat Nong+ Pla NiL FC</t>
+          <t>ผู้บ่าวไทบ้าน</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Piyabut Promrungruang</t>
+          <t>Thanit Sophajit</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E28" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
@@ -2262,19 +2262,19 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Winning Standard FC</t>
+          <t>Tengen El Paso</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Maytapat Yurawattarapon</t>
+          <t>EL Paso slow-bar Coffee</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E29" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
@@ -2320,19 +2320,19 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>eakachai@romeO</t>
+          <t>Wat Nong+ Pla NiL FC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Eakachai Hamhomvong</t>
+          <t>Piyabut Promrungruang</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E30" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
@@ -2378,19 +2378,19 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>KingPro</t>
+          <t>Winning Standard FC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>จิรวัฒน์ ขนอม</t>
+          <t>Maytapat Yurawattarapon</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E31" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
@@ -2436,19 +2436,19 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DATE26th</t>
+          <t>Aruch's Team</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Prarunya Kamahayung</t>
+          <t>Aruch Changthong</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E32" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
@@ -2494,19 +2494,19 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Marcomon FC</t>
+          <t>Raminthra Classic FC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Montri Chamchuklin</t>
+          <t>Chaichana Pathomekmongkhon</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E33" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
@@ -2552,19 +2552,19 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Aruch's Team</t>
+          <t>eakachai@romeO</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Aruch Changthong</t>
+          <t>Eakachai Hamhomvong</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E34" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
@@ -2610,19 +2610,19 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Wayuchocolate</t>
+          <t>KingPro</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ponlakit Choeychang</t>
+          <t>จิรวัฒน์ ขนอม</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E35" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
@@ -2668,19 +2668,19 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JK Blookner Olivera</t>
+          <t>onelove2499</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tanawut Polchamni</t>
+          <t>Mongkhol Namsang</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E36" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
@@ -2726,19 +2726,19 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Notta</t>
+          <t>Wayuchocolate</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jirawat Ritnamkham</t>
+          <t>Ponlakit Choeychang</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E37" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
@@ -2784,19 +2784,19 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Okaynaja</t>
+          <t>DATE26th</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sir Okaynaja</t>
+          <t>Prarunya Kamahayung</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E38" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
@@ -2842,19 +2842,19 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>onelove2499</t>
+          <t>JK Blookner Olivera</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Mongkhol Namsang</t>
+          <t>Tanawut Polchamni</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E39" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
@@ -2900,19 +2900,19 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Raminthra Classic FC</t>
+          <t>Okaynaja</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chaichana Pathomekmongkhon</t>
+          <t>Sir Okaynaja</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E40" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E41" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
@@ -3016,19 +3016,19 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>US TM</t>
+          <t>Pending Moderation</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>rawat rummamai</t>
+          <t>Sukit Mattanaweerapong</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E42" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
@@ -3074,19 +3074,19 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Pending Moderation</t>
+          <t>US TM</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sukit Mattanaweerapong</t>
+          <t>rawat rummamai</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E43" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E44" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
@@ -3199,10 +3199,10 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E45" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
@@ -3519,29 +3519,29 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Untapan</t>
+          <t>Lek C King</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Pakpong L.</t>
+          <t>Banyawake Tharnthong</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bench Boost (BB)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -3549,15 +3549,15 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>© B.Fernandes (4 pts)</t>
+          <t>© Rice (6 pts)</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>ใช้ BB -&gt; หักสำรอง 4 คน [Kinsky(2), Kerkez(0), Xhaka(9), Bogle(6)]</t>
+          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
         </is>
       </c>
     </row>
@@ -3566,33 +3566,33 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dogor Dorgu</t>
+          <t>Untapan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Piyapong Hongsuwan</t>
+          <t>Pakpong L.</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Bench Boost (BB)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -3600,11 +3600,11 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
+          <t>แพ้ไทเบรกเกอร์กัปตัน (4 vs 6)</t>
         </is>
       </c>
     </row>
@@ -3613,33 +3613,33 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sittinon's Team</t>
+          <t>IS_AK 18</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sittinon Temsongsai</t>
+          <t>อิทธิวัฒน์ คำภา</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Bench Boost (BB)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -3647,11 +3647,11 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>แพ้ไทเบรกเกอร์สำรอง (7 vs 9)</t>
+          <t>แพ้ไทเบรกเกอร์สำรอง (6 vs 17)</t>
         </is>
       </c>
     </row>
@@ -3660,20 +3660,20 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RiceCooker</t>
+          <t>Dogor Dorgu</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Chaiwat Munkong</t>
+          <t>Piyapong Hongsuwan</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -3686,15 +3686,15 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>© Gabriel (10 pts)</t>
+          <t>© B.Fernandes (4 pts)</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -3707,20 +3707,20 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Al-Nuser</t>
+          <t>Sittinon's Team</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Witsanu Munfak</t>
+          <t>Sittinon Temsongsai</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -3741,11 +3741,11 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>แพ้ไทเบรกเกอร์กัปตัน (4 vs 10)</t>
+          <t>แพ้ไทเบรกเกอร์สำรอง (7 vs 9)</t>
         </is>
       </c>
     </row>
@@ -3754,20 +3754,20 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>อนุบาลห้วยทับทัน</t>
+          <t>RiceCooker</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Chinnaarch Thanapongphasin</t>
+          <t>Chaiwat Munkong</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -3780,15 +3780,15 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>© B.Fernandes (4 pts)</t>
+          <t>© Gabriel (10 pts)</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -3801,20 +3801,20 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>APHICHAI  FC</t>
+          <t>Al-Nuser</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Aphichai Chanasook</t>
+          <t>Witsanu Munfak</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -3827,19 +3827,19 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>© Mbeumo (4 pts)</t>
+          <t>© Haaland (4 pts)</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
+          <t>แพ้ไทเบรกเกอร์กัปตัน (4 vs 10)</t>
         </is>
       </c>
     </row>
@@ -3848,20 +3848,20 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lek C King</t>
+          <t>อนุบาลห้วยทับทัน</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Banyawake Tharnthong</t>
+          <t>Chinnaarch Thanapongphasin</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3874,15 +3874,15 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>© Rice (6 pts)</t>
+          <t>© B.Fernandes (4 pts)</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -3895,20 +3895,20 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>รถซื้อแกง จะแรงได้ไง</t>
+          <t>Yenzo</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Nuttapong Limadisai</t>
+          <t>Xabi Alonso</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -3929,11 +3929,11 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>แพ้ไทเบรกเกอร์กัปตัน (4 vs 6)</t>
+          <t>🎲 แต้มเท่ากันทุกเกณฑ์ (ต้องจับฉลาก)</t>
         </is>
       </c>
     </row>
@@ -3942,20 +3942,20 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>N. DE JOE</t>
+          <t>APHICHAI  FC</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Nawapon Dechabun</t>
+          <t>Aphichai Chanasook</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3968,19 +3968,19 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>© Haaland (4 pts)</t>
+          <t>© Mbeumo (4 pts)</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>แพ้ไทเบรกเกอร์สำรอง (3 vs 15)</t>
+          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -4036,20 +4036,20 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ทีมของ Kritsada</t>
+          <t>รถซื้อแกง จะแรงได้ไง</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Kritsada saejueng</t>
+          <t>Nuttapong Limadisai</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -4062,15 +4062,15 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>© B.Fernandes (4 pts)</t>
+          <t>© Haaland (4 pts)</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -4083,20 +4083,20 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yenzo</t>
+          <t>N. DE JOE</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Xabi Alonso</t>
+          <t>Nawapon Dechabun</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -4117,11 +4117,11 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>แพ้ไทเบรกเกอร์สำรอง (10 vs 12)</t>
+          <t>แพ้ไทเบรกเกอร์สำรอง (3 vs 15)</t>
         </is>
       </c>
     </row>
@@ -4130,20 +4130,20 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nuttawut's Team</t>
+          <t>ทีมของ Kritsada</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Nuttawut Chutipong</t>
+          <t>Kritsada saejueng</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -4156,15 +4156,15 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>© Saka (18 pts)</t>
+          <t>© B.Fernandes (4 pts)</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -4177,20 +4177,20 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>C-KING</t>
+          <t>Pimson Team</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Theera Tiawilai</t>
+          <t>Chanwit Pimson</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4203,11 +4203,11 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>© B.Fernandes (4 pts)</t>
+          <t>© Haaland (4 pts)</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>แพ้ไทเบรกเกอร์กัปตัน (4 vs 18)</t>
+          <t>แพ้ไทเบรกเกอร์สำรอง (3 vs 12)</t>
         </is>
       </c>
     </row>
@@ -4224,20 +4224,20 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ผู้บ่าวไทบ้าน</t>
+          <t>Nuttawut's Team</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Thanit Sophajit</t>
+          <t>Nuttawut Chutipong</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4250,15 +4250,15 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>© Haaland (4 pts)</t>
+          <t>© Saka (18 pts)</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -4271,20 +4271,20 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tengen El Paso</t>
+          <t>C-KING</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>EL Paso slow-bar Coffee</t>
+          <t>Theera Tiawilai</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4297,19 +4297,19 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>© Haaland (4 pts)</t>
+          <t>© B.Fernandes (4 pts)</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>แพ้ไทเบรกเกอร์สำรอง (25 vs 29)</t>
+          <t>แพ้ไทเบรกเกอร์กัปตัน (4 vs 18)</t>
         </is>
       </c>
     </row>
@@ -4318,45 +4318,45 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>IS_AK 18</t>
+          <t>Marcomon FC</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>อิทธิวัฒน์ คำภา</t>
+          <t>Montri Chamchuklin</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bench Boost (BB)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>© Haaland (4 pts)</t>
+          <t>© Semenyo (4 pts)</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>แพ้ไทเบรกเกอร์สำรอง (17 vs 25)</t>
+          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
         </is>
       </c>
     </row>
@@ -4365,16 +4365,16 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pimson Team</t>
+          <t>ผู้บ่าวไทบ้าน</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Chanwit Pimson</t>
+          <t>Thanit Sophajit</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -4399,11 +4399,11 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>แพ้ไทเบรกเกอร์สำรอง (6 vs 17)</t>
+          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
         </is>
       </c>
     </row>
@@ -4412,20 +4412,20 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Wat Nong+ Pla NiL FC</t>
+          <t>Tengen El Paso</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Piyabut Promrungruang</t>
+          <t>EL Paso slow-bar Coffee</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -4446,11 +4446,11 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
+          <t>แพ้ไทเบรกเกอร์สำรอง (25 vs 29)</t>
         </is>
       </c>
     </row>
@@ -4459,20 +4459,20 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Winning Standard FC</t>
+          <t>Notta</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Maytapat Yurawattarapon</t>
+          <t>Jirawat Ritnamkham</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4485,19 +4485,19 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>© B.Fernandes (4 pts)</t>
+          <t>© Haaland (4 pts)</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
+          <t>แพ้ไทเบรกเกอร์สำรอง (2 vs 25)</t>
         </is>
       </c>
     </row>
@@ -4506,45 +4506,45 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PheT9</t>
+          <t>Aruch's Team</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Phachara Wannarat</t>
+          <t>Aruch Changthong</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bench Boost (BB)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>© B.Fernandes (4 pts)</t>
+          <t>© Rice (6 pts)</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>ใช้ BB -&gt; หักสำรอง 4 คน [Lammens(1), Palestra(0), Davis(2), Ndiaye(9)]</t>
+          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
         </is>
       </c>
     </row>
@@ -4557,16 +4557,16 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>eakachai@romeO</t>
+          <t>Wat Nong+ Pla NiL FC</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Eakachai Hamhomvong</t>
+          <t>Piyabut Promrungruang</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4579,19 +4579,19 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>© B.Fernandes (4 pts)</t>
+          <t>© Haaland (4 pts)</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>แพ้ไทเบรกเกอร์สำรอง (3 vs 12)</t>
+          <t>แพ้ไทเบรกเกอร์กัปตัน (4 vs 6)</t>
         </is>
       </c>
     </row>
@@ -4600,20 +4600,20 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>KingPro</t>
+          <t>Winning Standard FC</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>จิรวัฒน์ ขนอม</t>
+          <t>Maytapat Yurawattarapon</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4626,19 +4626,19 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>© Haaland (4 pts)</t>
+          <t>© B.Fernandes (4 pts)</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
+          <t>แพ้ไทเบรกเกอร์สำรอง (3 vs 14)</t>
         </is>
       </c>
     </row>
@@ -4647,20 +4647,20 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DATE26th</t>
+          <t>Raminthra Classic FC</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Prarunya Kamahayung</t>
+          <t>Chaichana Pathomekmongkhon</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4673,19 +4673,19 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>© Saka (18 pts)</t>
+          <t>© Gyökeres (0 pts)</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
+          <t>แพ้ไทเบรกเกอร์กัปตัน (0 vs 4)</t>
         </is>
       </c>
     </row>
@@ -4694,45 +4694,45 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Aruch's Team</t>
+          <t>PheT9</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Aruch Changthong</t>
+          <t>Phachara Wannarat</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Bench Boost (BB)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>© Rice (6 pts)</t>
+          <t>© B.Fernandes (4 pts)</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>แพ้ไทเบรกเกอร์กัปตัน (6 vs 18)</t>
+          <t>ใช้ BB -&gt; หักสำรอง 4 คน [Lammens(1), Palestra(0), Davis(2), Ndiaye(9)]</t>
         </is>
       </c>
     </row>
@@ -4741,20 +4741,20 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Marcomon FC</t>
+          <t>eakachai@romeO</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Montri Chamchuklin</t>
+          <t>Eakachai Hamhomvong</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4767,19 +4767,19 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>© Semenyo (4 pts)</t>
+          <t>© B.Fernandes (4 pts)</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>แพ้ไทเบรกเกอร์กัปตัน (4 vs 6)</t>
+          <t>แพ้ไทเบรกเกอร์สำรอง (3 vs 12)</t>
         </is>
       </c>
     </row>
@@ -4788,20 +4788,20 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Wayuchocolate</t>
+          <t>onelove2499</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Ponlakit Choeychang</t>
+          <t>Mongkhol Namsang</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4814,19 +4814,19 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>© Anderson (4 pts)</t>
+          <t>© Haaland (4 pts)</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>แพ้ไทเบรกเกอร์สำรอง (1 vs 14)</t>
+          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
         </is>
       </c>
     </row>
@@ -4835,33 +4835,33 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pending Moderation</t>
+          <t>KingPro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Piyanat Cherdchoo</t>
+          <t>จิรวัฒน์ ขนอม</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bench Boost (BB)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -4869,11 +4869,11 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>ใช้ BB -&gt; หักสำรอง 4 คน [Pickford(7), Richards(3), Jensen(6), Isidor(1)]</t>
+          <t>แพ้ไทเบรกเกอร์สำรอง (11 vs 12)</t>
         </is>
       </c>
     </row>
@@ -4882,20 +4882,20 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Notta</t>
+          <t>Wayuchocolate</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Jirawat Ritnamkham</t>
+          <t>Ponlakit Choeychang</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4908,19 +4908,19 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>© Haaland (4 pts)</t>
+          <t>© Anderson (4 pts)</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>แพ้ไทเบรกเกอร์สำรอง (12 vs 17)</t>
+          <t>แพ้ไทเบรกเกอร์สำรอง (0 vs 11)</t>
         </is>
       </c>
     </row>
@@ -4929,20 +4929,20 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>JK Blookner Olivera</t>
+          <t>DATE26th</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Tanawut Polchamni</t>
+          <t>Prarunya Kamahayung</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4955,19 +4955,19 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>© O'Reilly (4 pts)</t>
+          <t>© Saka (18 pts)</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>แพ้ไทเบรกเกอร์สำรอง (5 vs 12)</t>
+          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
         </is>
       </c>
     </row>
@@ -4976,45 +4976,45 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
+        <v>11</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Pending Moderation</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Piyanat Cherdchoo</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>54</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Bench Boost (BB)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-17</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
         <v>37</v>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Okaynaja</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Sir Okaynaja</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>36</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H37" t="n">
-        <v>36</v>
-      </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>© B.Fernandes (4 pts)</t>
+          <t>© Haaland (4 pts)</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
+          <t>ใช้ BB -&gt; หักสำรอง 4 คน [Pickford(7), Richards(3), Jensen(6), Isidor(1)]</t>
         </is>
       </c>
     </row>
@@ -5023,45 +5023,45 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>TanateR</t>
+          <t>JK Blookner Olivera</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ธเนศ รุจิ</t>
+          <t>Tanawut Polchamni</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bench Boost (BB)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-38</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>© B.Fernandes (4 pts)</t>
+          <t>© O'Reilly (4 pts)</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>ใช้ BB -&gt; หักสำรอง 4 คน [Verbruggen(6), João Pedro(11), Gakpo(12), Gvardiol(9)]</t>
+          <t>แพ้ไทเบรกเกอร์สำรอง (5 vs 17)</t>
         </is>
       </c>
     </row>
@@ -5070,20 +5070,20 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>onelove2499</t>
+          <t>Okaynaja</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Mongkhol Namsang</t>
+          <t>Sir Okaynaja</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5096,15 +5096,15 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>© Haaland (4 pts)</t>
+          <t>© B.Fernandes (4 pts)</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5117,45 +5117,45 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
+        <v>2</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>TanateR</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ธเนศ รุจิ</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>73</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Bench Boost (BB)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-38</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>35</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>© B.Fernandes (4 pts)</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
         <v>38</v>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Raminthra Classic FC</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Chaichana Pathomekmongkhon</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>34</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H40" t="n">
-        <v>34</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>© Gyökeres (0 pts)</t>
-        </is>
-      </c>
-      <c r="J40" t="n">
-        <v>5</v>
-      </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>แพ้ไทเบรกเกอร์กัปตัน (0 vs 4)</t>
+          <t>ใช้ BB -&gt; หักสำรอง 4 คน [Verbruggen(6), João Pedro(11), Gakpo(12), Gvardiol(9)]</t>
         </is>
       </c>
     </row>
@@ -5177,7 +5177,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -5198,11 +5198,11 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>เล่นตามปกติ (ผ่านเกณฑ์)</t>
+          <t>แพ้ไทเบรกเกอร์สำรอง (5 vs 38)</t>
         </is>
       </c>
     </row>
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -5292,11 +5292,11 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>แพ้ไทเบรกเกอร์สำรอง (2 vs 7)</t>
+          <t>แพ้ไทเบรกเกอร์สำรอง (0 vs 5)</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5318,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -5964,19 +5964,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sittinon's Team</t>
+          <t>Lek C King</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sittinon Temsongsai</t>
+          <t>Banyawake Tharnthong</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E9" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -6030,12 +6030,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dogor Dorgu</t>
+          <t>Sittinon's Team</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Piyapong Hongsuwan</t>
+          <t>Sittinon Temsongsai</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -6096,19 +6096,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RiceCooker</t>
+          <t>Dogor Dorgu</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chaiwat Munkong</t>
+          <t>Piyapong Hongsuwan</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E11" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -6162,12 +6162,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pending Moderation</t>
+          <t>Al-Nuser</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Piyanat Cherdchoo</t>
+          <t>Witsanu Munfak</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PheT9</t>
+          <t>Pending Moderation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Phachara Wannarat</t>
+          <t>Piyanat Cherdchoo</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Al-Nuser</t>
+          <t>PheT9</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Witsanu Munfak</t>
+          <t>Phachara Wannarat</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -6360,19 +6360,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>อนุบาลห้วยทับทัน</t>
+          <t>RiceCooker</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chinnaarch Thanapongphasin</t>
+          <t>Chaiwat Munkong</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -6426,19 +6426,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>APHICHAI  FC</t>
+          <t>อนุบาลห้วยทับทัน</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Aphichai Chanasook</t>
+          <t>Chinnaarch Thanapongphasin</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E16" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -6492,19 +6492,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>รถซื้อแกง จะแรงได้ไง</t>
+          <t>Yenzo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nuttapong Limadisai</t>
+          <t>Xabi Alonso</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E17" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -6558,19 +6558,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lek C King</t>
+          <t>APHICHAI  FC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Banyawake Tharnthong</t>
+          <t>Aphichai Chanasook</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E18" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -6690,19 +6690,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Aofmook Fc</t>
+          <t>รถซื้อแกง จะแรงได้ไง</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tuntawat Juntun</t>
+          <t>Nuttapong Limadisai</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E20" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -6756,19 +6756,19 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Yenzo</t>
+          <t>Aofmook Fc</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Xabi Alonso</t>
+          <t>Tuntawat Juntun</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E21" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -6888,19 +6888,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nuttawut's Team</t>
+          <t>Pimson Team</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nuttawut Chutipong</t>
+          <t>Chanwit Pimson</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E23" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -7020,19 +7020,19 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Pimson Team</t>
+          <t>Nuttawut's Team</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chanwit Pimson</t>
+          <t>Nuttawut Chutipong</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E25" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -7086,19 +7086,19 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ผู้บ่าวไทบ้าน</t>
+          <t>Marcomon FC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Thanit Sophajit</t>
+          <t>Montri Chamchuklin</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E26" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -7152,12 +7152,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Tengen El Paso</t>
+          <t>Notta</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>EL Paso slow-bar Coffee</t>
+          <t>Jirawat Ritnamkham</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -7218,19 +7218,19 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Wat Nong+ Pla NiL FC</t>
+          <t>ผู้บ่าวไทบ้าน</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Piyabut Promrungruang</t>
+          <t>Thanit Sophajit</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E28" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -7284,19 +7284,19 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Winning Standard FC</t>
+          <t>Tengen El Paso</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Maytapat Yurawattarapon</t>
+          <t>EL Paso slow-bar Coffee</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E29" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -7350,19 +7350,19 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>eakachai@romeO</t>
+          <t>Wat Nong+ Pla NiL FC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Eakachai Hamhomvong</t>
+          <t>Piyabut Promrungruang</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E30" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -7416,19 +7416,19 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>KingPro</t>
+          <t>Winning Standard FC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>จิรวัฒน์ ขนอม</t>
+          <t>Maytapat Yurawattarapon</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E31" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -7482,19 +7482,19 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DATE26th</t>
+          <t>Aruch's Team</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Prarunya Kamahayung</t>
+          <t>Aruch Changthong</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E32" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -7548,19 +7548,19 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Marcomon FC</t>
+          <t>Raminthra Classic FC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Montri Chamchuklin</t>
+          <t>Chaichana Pathomekmongkhon</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E33" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -7614,19 +7614,19 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Aruch's Team</t>
+          <t>eakachai@romeO</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Aruch Changthong</t>
+          <t>Eakachai Hamhomvong</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E34" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -7680,19 +7680,19 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Wayuchocolate</t>
+          <t>KingPro</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ponlakit Choeychang</t>
+          <t>จิรวัฒน์ ขนอม</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E35" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -7746,19 +7746,19 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JK Blookner Olivera</t>
+          <t>onelove2499</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tanawut Polchamni</t>
+          <t>Mongkhol Namsang</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E36" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -7812,19 +7812,19 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Notta</t>
+          <t>Wayuchocolate</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jirawat Ritnamkham</t>
+          <t>Ponlakit Choeychang</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E37" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -7878,19 +7878,19 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Okaynaja</t>
+          <t>DATE26th</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sir Okaynaja</t>
+          <t>Prarunya Kamahayung</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E38" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -7944,19 +7944,19 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>onelove2499</t>
+          <t>JK Blookner Olivera</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Mongkhol Namsang</t>
+          <t>Tanawut Polchamni</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E39" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -8010,19 +8010,19 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Raminthra Classic FC</t>
+          <t>Okaynaja</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chaichana Pathomekmongkhon</t>
+          <t>Sir Okaynaja</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E40" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -8085,10 +8085,10 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E41" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -8142,19 +8142,19 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>US TM</t>
+          <t>Pending Moderation</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>rawat rummamai</t>
+          <t>Sukit Mattanaweerapong</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E42" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -8208,19 +8208,19 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Pending Moderation</t>
+          <t>US TM</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sukit Mattanaweerapong</t>
+          <t>rawat rummamai</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E43" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -8283,10 +8283,10 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E44" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -8349,10 +8349,10 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E45" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -8681,12 +8681,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sittinon's Team</t>
+          <t>Lek C King</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sittinon Temsongsai</t>
+          <t>Banyawake Tharnthong</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -8713,12 +8713,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Dogor Dorgu</t>
+          <t>Sittinon's Team</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Piyapong Hongsuwan</t>
+          <t>Sittinon Temsongsai</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -8745,12 +8745,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RiceCooker</t>
+          <t>Dogor Dorgu</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chaiwat Munkong</t>
+          <t>Piyapong Hongsuwan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -8777,12 +8777,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pending Moderation</t>
+          <t>Al-Nuser</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Piyanat Cherdchoo</t>
+          <t>Witsanu Munfak</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -8797,7 +8797,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>GW1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -8809,12 +8809,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PheT9</t>
+          <t>Pending Moderation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Phachara Wannarat</t>
+          <t>Piyanat Cherdchoo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -8841,12 +8841,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Al-Nuser</t>
+          <t>PheT9</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Witsanu Munfak</t>
+          <t>Phachara Wannarat</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GW1</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -8873,12 +8873,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>อนุบาลห้วยทับทัน</t>
+          <t>RiceCooker</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Chinnaarch Thanapongphasin</t>
+          <t>Chaiwat Munkong</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -8905,12 +8905,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>APHICHAI  FC</t>
+          <t>อนุบาลห้วยทับทัน</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Aphichai Chanasook</t>
+          <t>Chinnaarch Thanapongphasin</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -8937,12 +8937,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>รถซื้อแกง จะแรงได้ไง</t>
+          <t>Yenzo</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nuttapong Limadisai</t>
+          <t>Xabi Alonso</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -8969,12 +8969,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Lek C King</t>
+          <t>APHICHAI  FC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Banyawake Tharnthong</t>
+          <t>Aphichai Chanasook</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -9033,12 +9033,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Aofmook Fc</t>
+          <t>รถซื้อแกง จะแรงได้ไง</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tuntawat Juntun</t>
+          <t>Nuttapong Limadisai</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -9065,12 +9065,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Yenzo</t>
+          <t>Aofmook Fc</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Xabi Alonso</t>
+          <t>Tuntawat Juntun</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -9129,12 +9129,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nuttawut's Team</t>
+          <t>Pimson Team</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nuttawut Chutipong</t>
+          <t>Chanwit Pimson</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -9193,12 +9193,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Pimson Team</t>
+          <t>Nuttawut's Team</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Chanwit Pimson</t>
+          <t>Nuttawut Chutipong</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -9225,12 +9225,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ผู้บ่าวไทบ้าน</t>
+          <t>Marcomon FC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Thanit Sophajit</t>
+          <t>Montri Chamchuklin</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -9257,12 +9257,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Tengen El Paso</t>
+          <t>Notta</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>EL Paso slow-bar Coffee</t>
+          <t>Jirawat Ritnamkham</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -9289,12 +9289,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Wat Nong+ Pla NiL FC</t>
+          <t>ผู้บ่าวไทบ้าน</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Piyabut Promrungruang</t>
+          <t>Thanit Sophajit</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -9321,12 +9321,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Winning Standard FC</t>
+          <t>Tengen El Paso</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Maytapat Yurawattarapon</t>
+          <t>EL Paso slow-bar Coffee</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -9353,12 +9353,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>eakachai@romeO</t>
+          <t>Wat Nong+ Pla NiL FC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Eakachai Hamhomvong</t>
+          <t>Piyabut Promrungruang</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -9385,12 +9385,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>KingPro</t>
+          <t>Winning Standard FC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>จิรวัฒน์ ขนอม</t>
+          <t>Maytapat Yurawattarapon</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -9417,12 +9417,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DATE26th</t>
+          <t>Aruch's Team</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Prarunya Kamahayung</t>
+          <t>Aruch Changthong</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -9449,12 +9449,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Marcomon FC</t>
+          <t>Raminthra Classic FC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Montri Chamchuklin</t>
+          <t>Chaichana Pathomekmongkhon</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -9481,12 +9481,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Aruch's Team</t>
+          <t>eakachai@romeO</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Aruch Changthong</t>
+          <t>Eakachai Hamhomvong</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -9513,12 +9513,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Wayuchocolate</t>
+          <t>KingPro</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ponlakit Choeychang</t>
+          <t>จิรวัฒน์ ขนอม</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -9545,12 +9545,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>JK Blookner Olivera</t>
+          <t>onelove2499</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tanawut Polchamni</t>
+          <t>Mongkhol Namsang</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -9577,12 +9577,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Notta</t>
+          <t>Wayuchocolate</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Jirawat Ritnamkham</t>
+          <t>Ponlakit Choeychang</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -9609,12 +9609,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Okaynaja</t>
+          <t>DATE26th</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sir Okaynaja</t>
+          <t>Prarunya Kamahayung</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -9641,12 +9641,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>onelove2499</t>
+          <t>JK Blookner Olivera</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mongkhol Namsang</t>
+          <t>Tanawut Polchamni</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -9673,12 +9673,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Raminthra Classic FC</t>
+          <t>Okaynaja</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Chaichana Pathomekmongkhon</t>
+          <t>Sir Okaynaja</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -9737,12 +9737,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>US TM</t>
+          <t>Pending Moderation</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>rawat rummamai</t>
+          <t>Sukit Mattanaweerapong</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -9769,12 +9769,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Pending Moderation</t>
+          <t>US TM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Sukit Mattanaweerapong</t>
+          <t>rawat rummamai</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
